--- a/Data for R/DOP/DOP EDI Qry_Presence_Absence Categories to Post.xlsx
+++ b/Data for R/DOP/DOP EDI Qry_Presence_Absence Categories to Post.xlsx
@@ -14313,7 +14313,7 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>20mm</t>
         </is>
       </c>
       <c r="D153" s="6">
@@ -14340,9 +14340,21 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J153" s="8">
+        <v>0.492997685185185</v>
+      </c>
+      <c r="K153" s="9">
+        <v>26.7</v>
+      </c>
+      <c r="L153" s="9">
+        <v>16</v>
+      </c>
+      <c r="M153" s="9">
+        <v>3596</v>
+      </c>
       <c r="N153" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>1.87</t>
         </is>
       </c>
       <c r="Q153" s="9" t="inlineStr">
@@ -14352,8 +14364,11 @@
       </c>
       <c r="R153" s="9" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S153" s="9">
+        <v>119</v>
       </c>
       <c r="T153" s="9">
         <v>0.0076</v>
@@ -14362,6 +14377,9 @@
         <is>
           <t>Y</t>
         </is>
+      </c>
+      <c r="V153" s="10">
+        <v>15.7</v>
       </c>
       <c r="X153" s="11">
         <v>1</v>
@@ -14476,7 +14494,7 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>20mm</t>
         </is>
       </c>
       <c r="D155" s="6">
@@ -14503,9 +14521,21 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J155" s="8">
+        <v>0.406956018518519</v>
+      </c>
+      <c r="K155" s="9">
+        <v>14.3</v>
+      </c>
+      <c r="L155" s="9">
+        <v>16.9</v>
+      </c>
+      <c r="M155" s="9">
+        <v>656</v>
+      </c>
       <c r="N155" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.30</t>
         </is>
       </c>
       <c r="Q155" s="9" t="inlineStr">
@@ -14515,8 +14545,11 @@
       </c>
       <c r="R155" s="9" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S155" s="9">
+        <v>68.4</v>
       </c>
       <c r="T155" s="9">
         <v>0.1542</v>
@@ -14525,6 +14558,9 @@
         <is>
           <t>Y</t>
         </is>
+      </c>
+      <c r="V155" s="10">
+        <v>29.1</v>
       </c>
       <c r="W155" s="9">
         <v>0.00057</v>

--- a/Data for R/DOP/DOP EDI Qry_Presence_Absence Categories to Post.xlsx
+++ b/Data for R/DOP/DOP EDI Qry_Presence_Absence Categories to Post.xlsx
@@ -11725,7 +11725,7 @@
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>L0493</t>
+          <t>0493</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -11750,9 +11750,15 @@
           <t>0.37</t>
         </is>
       </c>
+      <c r="O123" s="9">
+        <v>18.3</v>
+      </c>
+      <c r="P123" s="9">
+        <v>786</v>
+      </c>
       <c r="Q123" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.37</t>
         </is>
       </c>
       <c r="R123" s="9" t="inlineStr">
@@ -11814,7 +11820,7 @@
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>L0448</t>
+          <t>448</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -11839,9 +11845,15 @@
           <t>0.06</t>
         </is>
       </c>
+      <c r="O124" s="9">
+        <v>13.9</v>
+      </c>
+      <c r="P124" s="9">
+        <v>137.5</v>
+      </c>
       <c r="Q124" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.06</t>
         </is>
       </c>
       <c r="R124" s="9" t="inlineStr">
@@ -11903,7 +11915,7 @@
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>L1361</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -11925,9 +11937,15 @@
           <t>0.34</t>
         </is>
       </c>
+      <c r="O125" s="9">
+        <v>17.4</v>
+      </c>
+      <c r="P125" s="9">
+        <v>737</v>
+      </c>
       <c r="Q125" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.34</t>
         </is>
       </c>
       <c r="R125" s="9" t="inlineStr">
@@ -11989,7 +12007,7 @@
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>Vial 1</t>
+          <t>LV1</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -12549,8 +12567,14 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J132" s="8">
+        <v>0.386805555555556</v>
+      </c>
+      <c r="K132" s="9">
+        <v>17.3</v>
+      </c>
       <c r="L132" s="9">
-        <v>8.60000038146973</v>
+        <v>8.600000381</v>
       </c>
       <c r="M132" s="9">
         <v>410</v>
@@ -12567,11 +12591,11 @@
       </c>
       <c r="R132" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>31</t>
         </is>
       </c>
       <c r="S132" s="9">
-        <v>37.5999984741211</v>
+        <v>37.59999847</v>
       </c>
       <c r="T132" s="9">
         <v>1.2486</v>
@@ -12635,8 +12659,14 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J133" s="8">
+        <v>0.431944444444444</v>
+      </c>
+      <c r="K133" s="9">
+        <v>11.3</v>
+      </c>
       <c r="L133" s="9">
-        <v>10.6000003814697</v>
+        <v>10.60000038</v>
       </c>
       <c r="M133" s="9">
         <v>1113</v>
@@ -12653,7 +12683,7 @@
       </c>
       <c r="R133" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>131</t>
         </is>
       </c>
       <c r="S133" s="9">
@@ -12721,8 +12751,14 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J134" s="8">
+        <v>0.402083333333333</v>
+      </c>
+      <c r="K134" s="9">
+        <v>9.8</v>
+      </c>
       <c r="L134" s="9">
-        <v>8.80000019073486</v>
+        <v>8.800000191</v>
       </c>
       <c r="M134" s="9">
         <v>541</v>
@@ -12739,11 +12775,11 @@
       </c>
       <c r="R134" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>34</t>
         </is>
       </c>
       <c r="S134" s="9">
-        <v>38.7999992370605</v>
+        <v>38.79999924</v>
       </c>
       <c r="T134" s="9">
         <v>4.227</v>
@@ -12887,8 +12923,14 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J136" s="8">
+        <v>0.348611111111111</v>
+      </c>
+      <c r="K136" s="9">
+        <v>10.1</v>
+      </c>
       <c r="L136" s="9">
-        <v>9.80000019073486</v>
+        <v>9.800000191</v>
       </c>
       <c r="M136" s="9">
         <v>639</v>
@@ -12909,7 +12951,7 @@
         </is>
       </c>
       <c r="S136" s="9">
-        <v>75.0999984741211</v>
+        <v>75.09999847</v>
       </c>
       <c r="T136" s="9">
         <v>2.5888</v>
@@ -12973,11 +13015,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J137" s="8">
+        <v>0.408333333333333</v>
+      </c>
+      <c r="K137" s="9">
+        <v>11.3</v>
+      </c>
       <c r="L137" s="9">
-        <v>9.69999980926514</v>
+        <v>9.699999809</v>
       </c>
       <c r="M137" s="9">
-        <v>232.100006103516</v>
+        <v>232.1000061</v>
       </c>
       <c r="N137" s="9" t="inlineStr">
         <is>
@@ -12995,7 +13043,7 @@
         </is>
       </c>
       <c r="S137" s="9">
-        <v>32.2999992370605</v>
+        <v>32.29999924</v>
       </c>
       <c r="T137" s="9">
         <v>6.6357</v>
@@ -13146,10 +13194,10 @@
         <v>11.1</v>
       </c>
       <c r="L139" s="9">
-        <v>22.1000003814697</v>
+        <v>22.10000038</v>
       </c>
       <c r="M139" s="9">
-        <v>323.600006103516</v>
+        <v>323.6000061</v>
       </c>
       <c r="N139" s="9" t="inlineStr">
         <is>
@@ -13231,8 +13279,14 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J140" s="8">
+        <v>0.431944444444444</v>
+      </c>
+      <c r="K140" s="9">
+        <v>4.7</v>
+      </c>
       <c r="L140" s="9">
-        <v>10.1000003814697</v>
+        <v>10.10000038</v>
       </c>
       <c r="M140" s="9">
         <v>3131</v>
@@ -13253,7 +13307,7 @@
         </is>
       </c>
       <c r="S140" s="9">
-        <v>25.1000003814697</v>
+        <v>25.10000038</v>
       </c>
       <c r="T140" s="9">
         <v>3.6947</v>
@@ -13290,7 +13344,7 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>KT</t>
         </is>
       </c>
       <c r="D141" s="6">
@@ -13309,13 +13363,16 @@
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>0011</t>
+          <t>S-011</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
           <t>DELSME</t>
         </is>
+      </c>
+      <c r="J141" s="8">
+        <v>0.513888888888889</v>
       </c>
       <c r="N141" s="9" t="inlineStr">
         <is>
@@ -13339,6 +13396,9 @@
         <is>
           <t>Y</t>
         </is>
+      </c>
+      <c r="V141" s="10">
+        <v>68</v>
       </c>
       <c r="W141" s="9">
         <v>0.0296</v>
@@ -13391,8 +13451,14 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J142" s="8">
+        <v>0.51875</v>
+      </c>
+      <c r="K142" s="9">
+        <v>6.8</v>
+      </c>
       <c r="L142" s="9">
-        <v>15.3999996185303</v>
+        <v>15.39999962</v>
       </c>
       <c r="M142" s="9">
         <v>4335</v>
@@ -13413,7 +13479,7 @@
         </is>
       </c>
       <c r="S142" s="9">
-        <v>90.4000015258789</v>
+        <v>90.40000153</v>
       </c>
       <c r="T142" s="9">
         <v>2.694</v>
@@ -13477,6 +13543,12 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J143" s="8">
+        <v>0.465972222222222</v>
+      </c>
+      <c r="K143" s="9">
+        <v>8.8</v>
+      </c>
       <c r="L143" s="9">
         <v>16.5</v>
       </c>
@@ -13499,7 +13571,7 @@
         </is>
       </c>
       <c r="S143" s="9">
-        <v>93.6999969482422</v>
+        <v>93.69999695</v>
       </c>
       <c r="T143" s="9">
         <v>2.7079</v>
@@ -13563,11 +13635,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J144" s="8">
+        <v>0.520138888888889</v>
+      </c>
+      <c r="K144" s="9">
+        <v>11</v>
+      </c>
       <c r="L144" s="9">
-        <v>11.1999998092651</v>
+        <v>11.19999981</v>
       </c>
       <c r="M144" s="9">
-        <v>386.799987792969</v>
+        <v>386.7999878</v>
       </c>
       <c r="N144" s="9" t="inlineStr">
         <is>
@@ -13585,7 +13663,7 @@
         </is>
       </c>
       <c r="S144" s="9">
-        <v>25.6000003814697</v>
+        <v>25.60000038</v>
       </c>
       <c r="T144" s="9">
         <v>3.8923</v>
@@ -13649,11 +13727,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J145" s="8">
+        <v>0.520138888888889</v>
+      </c>
+      <c r="K145" s="9">
+        <v>11</v>
+      </c>
       <c r="L145" s="9">
-        <v>11.1999998092651</v>
+        <v>11.19999981</v>
       </c>
       <c r="M145" s="9">
-        <v>386.799987792969</v>
+        <v>386.7999878</v>
       </c>
       <c r="N145" s="9" t="inlineStr">
         <is>
@@ -13671,7 +13755,7 @@
         </is>
       </c>
       <c r="S145" s="9">
-        <v>25.6000003814697</v>
+        <v>25.60000038</v>
       </c>
       <c r="T145" s="9">
         <v>1.3369</v>
@@ -13735,11 +13819,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J146" s="8">
+        <v>0.520138888888889</v>
+      </c>
+      <c r="K146" s="9">
+        <v>11</v>
+      </c>
       <c r="L146" s="9">
-        <v>11.1999998092651</v>
+        <v>11.19999981</v>
       </c>
       <c r="M146" s="9">
-        <v>386.799987792969</v>
+        <v>386.7999878</v>
       </c>
       <c r="N146" s="9" t="inlineStr">
         <is>
@@ -13757,7 +13847,7 @@
         </is>
       </c>
       <c r="S146" s="9">
-        <v>25.6000003814697</v>
+        <v>25.60000038</v>
       </c>
       <c r="T146" s="9">
         <v>1.8949</v>
@@ -13821,6 +13911,12 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J147" s="8">
+        <v>0.532638888888889</v>
+      </c>
+      <c r="K147" s="9">
+        <v>10.8</v>
+      </c>
       <c r="L147" s="9">
         <v>11</v>
       </c>
@@ -13843,7 +13939,7 @@
         </is>
       </c>
       <c r="S147" s="9">
-        <v>30.1000003814697</v>
+        <v>30.10000038</v>
       </c>
       <c r="T147" s="9">
         <v>1.7369</v>
@@ -13907,11 +14003,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J148" s="8">
+        <v>0.428472222222222</v>
+      </c>
+      <c r="K148" s="9">
+        <v>7.6</v>
+      </c>
       <c r="L148" s="9">
-        <v>12.1999998092651</v>
+        <v>12.19999981</v>
       </c>
       <c r="M148" s="9">
-        <v>433.899993896484</v>
+        <v>433.8999939</v>
       </c>
       <c r="N148" s="9" t="inlineStr">
         <is>
@@ -13929,7 +14031,7 @@
         </is>
       </c>
       <c r="S148" s="9">
-        <v>27.2000007629395</v>
+        <v>27.20000076</v>
       </c>
       <c r="T148" s="9">
         <v>2.1016</v>
@@ -13993,11 +14095,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J149" s="8">
+        <v>0.428472222222222</v>
+      </c>
+      <c r="K149" s="9">
+        <v>7.6</v>
+      </c>
       <c r="L149" s="9">
-        <v>12.1999998092651</v>
+        <v>12.19999981</v>
       </c>
       <c r="M149" s="9">
-        <v>433.899993896484</v>
+        <v>433.8999939</v>
       </c>
       <c r="N149" s="9" t="inlineStr">
         <is>
@@ -14015,7 +14123,7 @@
         </is>
       </c>
       <c r="S149" s="9">
-        <v>27.2000007629395</v>
+        <v>27.20000076</v>
       </c>
       <c r="T149" s="9">
         <v>1.011</v>
@@ -14079,11 +14187,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J150" s="8">
+        <v>0.428472222222222</v>
+      </c>
+      <c r="K150" s="9">
+        <v>7.6</v>
+      </c>
       <c r="L150" s="9">
-        <v>12.1999998092651</v>
+        <v>12.19999981</v>
       </c>
       <c r="M150" s="9">
-        <v>433.899993896484</v>
+        <v>433.8999939</v>
       </c>
       <c r="N150" s="9" t="inlineStr">
         <is>
@@ -14101,7 +14215,7 @@
         </is>
       </c>
       <c r="S150" s="9">
-        <v>27.2000007629395</v>
+        <v>27.20000076</v>
       </c>
       <c r="T150" s="9">
         <v>1.8063</v>
@@ -14168,11 +14282,17 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J151" s="8">
+        <v>0.428472222222222</v>
+      </c>
+      <c r="K151" s="9">
+        <v>7.6</v>
+      </c>
       <c r="L151" s="9">
-        <v>12.1999998092651</v>
+        <v>12.19999981</v>
       </c>
       <c r="M151" s="9">
-        <v>433.899993896484</v>
+        <v>433.8999939</v>
       </c>
       <c r="N151" s="9" t="inlineStr">
         <is>
@@ -14190,7 +14310,7 @@
         </is>
       </c>
       <c r="S151" s="9">
-        <v>27.2000007629395</v>
+        <v>27.20000076</v>
       </c>
       <c r="T151" s="9">
         <v>3.5917</v>
@@ -14257,6 +14377,12 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J152" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="K152" s="9">
+        <v>7.4</v>
+      </c>
       <c r="L152" s="9">
         <v>14.5</v>
       </c>
@@ -14279,7 +14405,7 @@
         </is>
       </c>
       <c r="S152" s="9">
-        <v>26.7000007629395</v>
+        <v>26.70000076</v>
       </c>
       <c r="T152" s="9">
         <v>2.4354</v>
@@ -14344,7 +14470,7 @@
         <v>0.492997685185185</v>
       </c>
       <c r="K153" s="9">
-        <v>26.7</v>
+        <v>8.13816</v>
       </c>
       <c r="L153" s="9">
         <v>16</v>
@@ -14429,8 +14555,14 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J154" s="8">
+        <v>0.527777777777778</v>
+      </c>
+      <c r="K154" s="9">
+        <v>8.4</v>
+      </c>
       <c r="L154" s="9">
-        <v>23.2000007629395</v>
+        <v>23.20000076</v>
       </c>
       <c r="M154" s="9">
         <v>586</v>
@@ -14525,7 +14657,7 @@
         <v>0.406956018518519</v>
       </c>
       <c r="K155" s="9">
-        <v>14.3</v>
+        <v>4.35864</v>
       </c>
       <c r="L155" s="9">
         <v>16.9</v>
@@ -14613,6 +14745,12 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J156" s="8">
+        <v>0.365266203703704</v>
+      </c>
+      <c r="K156" s="9">
+        <v>7.1628</v>
+      </c>
       <c r="L156" s="9">
         <v>15.8</v>
       </c>
@@ -14699,11 +14837,14 @@
       <c r="J157" s="8">
         <v>0.365277777777778</v>
       </c>
+      <c r="K157" s="9">
+        <v>12.1</v>
+      </c>
       <c r="L157" s="9">
-        <v>8.19999980926514</v>
+        <v>8.199999809</v>
       </c>
       <c r="M157" s="9">
-        <v>169.600006103516</v>
+        <v>169.6000061</v>
       </c>
       <c r="N157" s="9" t="inlineStr">
         <is>
@@ -14719,6 +14860,9 @@
         <is>
           <t>14</t>
         </is>
+      </c>
+      <c r="S157" s="9">
+        <v>120</v>
       </c>
       <c r="T157" s="9">
         <v>4.1981</v>
@@ -15191,8 +15335,11 @@
       <c r="J163" s="8">
         <v>0.366666666666667</v>
       </c>
+      <c r="K163" s="9">
+        <v>3.9</v>
+      </c>
       <c r="L163" s="9">
-        <v>18.7999992370605</v>
+        <v>18.79999924</v>
       </c>
       <c r="M163" s="9">
         <v>6651</v>
@@ -15211,6 +15358,9 @@
         <is>
           <t>40</t>
         </is>
+      </c>
+      <c r="S163" s="9">
+        <v>41.5</v>
       </c>
       <c r="T163" s="9">
         <v>0.6435</v>
@@ -15277,8 +15427,11 @@
       <c r="J164" s="8">
         <v>0.461111111111111</v>
       </c>
+      <c r="K164" s="9">
+        <v>6.4</v>
+      </c>
       <c r="L164" s="9">
-        <v>19.6000003814697</v>
+        <v>19.60000038</v>
       </c>
       <c r="M164" s="9">
         <v>9420</v>
@@ -15297,6 +15450,9 @@
         <is>
           <t>31</t>
         </is>
+      </c>
+      <c r="S164" s="9">
+        <v>45.79999924</v>
       </c>
       <c r="T164" s="9">
         <v>2.0226</v>
@@ -15363,11 +15519,14 @@
       <c r="J165" s="8">
         <v>0.3875</v>
       </c>
+      <c r="K165" s="9">
+        <v>17.4</v>
+      </c>
       <c r="L165" s="9">
         <v>8.5</v>
       </c>
       <c r="M165" s="9">
-        <v>242.699996948242</v>
+        <v>242.6999969</v>
       </c>
       <c r="N165" s="9" t="inlineStr">
         <is>
@@ -15383,6 +15542,9 @@
         <is>
           <t>26</t>
         </is>
+      </c>
+      <c r="S165" s="9">
+        <v>47.70000076</v>
       </c>
       <c r="T165" s="9">
         <v>3.1539</v>

--- a/Data for R/DOP/DOP EDI Qry_Presence_Absence Categories to Post.xlsx
+++ b/Data for R/DOP/DOP EDI Qry_Presence_Absence Categories to Post.xlsx
@@ -643,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC186"/>
+  <dimension ref="A1:AE187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="11.328125"/>
@@ -671,10 +671,12 @@
     <col customWidth="true" min="23" max="23" width="26.8046875"/>
     <col customWidth="true" min="24" max="24" width="14.0625"/>
     <col customWidth="true" min="25" max="25" width="14.0625"/>
-    <col customWidth="true" min="26" max="26" width="14.0625"/>
-    <col customWidth="true" min="27" max="27" width="14.0625"/>
+    <col customWidth="true" min="26" max="26" width="10.10546875"/>
+    <col customWidth="true" min="27" max="27" width="10.984375"/>
     <col customWidth="true" min="28" max="28" width="14.0625"/>
     <col customWidth="true" min="29" max="29" width="14.0625"/>
+    <col customWidth="true" min="30" max="30" width="14.0625"/>
+    <col customWidth="true" min="31" max="31" width="14.0625"/>
   </cols>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -805,20 +807,30 @@
       </c>
       <c r="Z1" s="2" t="inlineStr">
         <is>
+          <t>DietStudy</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>PreyItemsID'd</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
           <t>Debris (sand/silt/mud)</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>Stomach/Gut Tissue</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Unid animal material</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Unid plant material</t>
         </is>
@@ -906,7 +918,15 @@
       <c r="Y2" s="11">
         <v>3</v>
       </c>
-      <c r="AB2" s="11">
+      <c r="Z2" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD2" s="11">
         <v>1</v>
       </c>
     </row>
@@ -995,7 +1015,15 @@
       <c r="Y3" s="11">
         <v>3</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="Z3" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD3" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1087,7 +1115,15 @@
       <c r="Z4" s="11">
         <v>1</v>
       </c>
-      <c r="AC4" s="11">
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB4" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1176,10 +1212,18 @@
       <c r="Y5" s="11">
         <v>2</v>
       </c>
-      <c r="AB5" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="11">
+      <c r="Z5" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD5" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1268,7 +1312,15 @@
       <c r="Z6" s="11">
         <v>1</v>
       </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AB6" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1354,7 +1406,15 @@
       <c r="Y7" s="11">
         <v>3</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="Z7" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD7" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1446,6 +1506,14 @@
       <c r="Z8" s="11">
         <v>1</v>
       </c>
+      <c r="AA8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB8" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="4">
@@ -1529,7 +1597,15 @@
       <c r="Y9" s="11">
         <v>3</v>
       </c>
-      <c r="AC9" s="11">
+      <c r="Z9" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE9" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1615,7 +1691,15 @@
       <c r="Y10" s="11">
         <v>3</v>
       </c>
-      <c r="AB10" s="11">
+      <c r="Z10" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD10" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1704,6 +1788,14 @@
       <c r="Z11" s="11">
         <v>1</v>
       </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB11" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="4">
@@ -1787,7 +1879,15 @@
       <c r="Y12" s="11">
         <v>2</v>
       </c>
-      <c r="AB12" s="11">
+      <c r="Z12" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD12" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1873,6 +1973,14 @@
       <c r="Z13" s="11">
         <v>1</v>
       </c>
+      <c r="AA13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB13" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="4">
@@ -1959,7 +2067,15 @@
       <c r="Y14" s="11">
         <v>3</v>
       </c>
-      <c r="AB14" s="11">
+      <c r="Z14" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD14" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2045,7 +2161,15 @@
       <c r="Y15" s="11">
         <v>3</v>
       </c>
-      <c r="AB15" s="11">
+      <c r="Z15" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD15" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2134,6 +2258,14 @@
       <c r="Z16" s="11">
         <v>1</v>
       </c>
+      <c r="AA16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB16" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="4">
@@ -2223,7 +2355,15 @@
       <c r="Z17" s="11">
         <v>1</v>
       </c>
-      <c r="AC17" s="11">
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB17" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2309,7 +2449,15 @@
       <c r="Y18" s="11">
         <v>3</v>
       </c>
-      <c r="AC18" s="11">
+      <c r="Z18" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE18" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2398,7 +2546,15 @@
       <c r="Y19" s="11">
         <v>2</v>
       </c>
-      <c r="AC19" s="11">
+      <c r="Z19" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE19" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2487,7 +2643,15 @@
       <c r="Y20" s="11">
         <v>3</v>
       </c>
-      <c r="AC20" s="11">
+      <c r="Z20" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE20" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2579,6 +2743,14 @@
       <c r="Z21" s="11">
         <v>1</v>
       </c>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB21" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="4">
@@ -2662,7 +2834,15 @@
       <c r="Y22" s="11">
         <v>3</v>
       </c>
-      <c r="AC22" s="11">
+      <c r="Z22" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE22" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2748,7 +2928,15 @@
       <c r="Y23" s="11">
         <v>3</v>
       </c>
-      <c r="AC23" s="11">
+      <c r="Z23" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE23" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2834,7 +3022,15 @@
       <c r="Y24" s="11">
         <v>3</v>
       </c>
-      <c r="AC24" s="11">
+      <c r="Z24" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE24" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2920,7 +3116,15 @@
       <c r="Y25" s="11">
         <v>2</v>
       </c>
-      <c r="AB25" s="11">
+      <c r="Z25" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD25" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3009,7 +3213,15 @@
       <c r="Z26" s="11">
         <v>1</v>
       </c>
-      <c r="AC26" s="11">
+      <c r="AA26" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB26" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3098,6 +3310,14 @@
       <c r="Z27" s="11">
         <v>1</v>
       </c>
+      <c r="AA27" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB27" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="4">
@@ -3184,7 +3404,15 @@
       <c r="Z28" s="11">
         <v>1</v>
       </c>
-      <c r="AC28" s="11">
+      <c r="AA28" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB28" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE28" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3270,7 +3498,15 @@
       <c r="Y29" s="11">
         <v>3</v>
       </c>
-      <c r="AC29" s="11">
+      <c r="Z29" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE29" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3359,7 +3595,15 @@
       <c r="Z30" s="11">
         <v>1</v>
       </c>
+      <c r="AA30" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AB30" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3445,7 +3689,15 @@
       <c r="Y31" s="11">
         <v>3</v>
       </c>
-      <c r="AC31" s="11">
+      <c r="Z31" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE31" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3522,7 +3774,15 @@
       <c r="Y32" s="11">
         <v>2</v>
       </c>
-      <c r="AC32" s="11">
+      <c r="Z32" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE32" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3608,7 +3868,15 @@
       <c r="Y33" s="11">
         <v>2</v>
       </c>
-      <c r="AC33" s="11">
+      <c r="Z33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE33" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3700,6 +3968,14 @@
       <c r="Z34" s="11">
         <v>1</v>
       </c>
+      <c r="AA34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB34" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="4">
@@ -3786,6 +4062,14 @@
       <c r="Z35" s="11">
         <v>1</v>
       </c>
+      <c r="AA35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB35" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="4">
@@ -3869,7 +4153,15 @@
       <c r="Y36" s="11">
         <v>2</v>
       </c>
-      <c r="AC36" s="11">
+      <c r="Z36" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE36" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3955,7 +4247,15 @@
       <c r="Y37" s="11">
         <v>2</v>
       </c>
-      <c r="AC37" s="11">
+      <c r="Z37" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE37" s="11">
         <v>2</v>
       </c>
     </row>
@@ -4041,7 +4341,15 @@
       <c r="Y38" s="11">
         <v>3</v>
       </c>
-      <c r="AB38" s="11">
+      <c r="Z38" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD38" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4127,10 +4435,18 @@
       <c r="Y39" s="11">
         <v>3</v>
       </c>
-      <c r="AB39" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="11">
+      <c r="Z39" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD39" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4219,7 +4535,15 @@
       <c r="Z40" s="11">
         <v>1</v>
       </c>
-      <c r="AC40" s="11">
+      <c r="AA40" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB40" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="11">
         <v>2</v>
       </c>
     </row>
@@ -4305,7 +4629,15 @@
       <c r="Y41" s="11">
         <v>3</v>
       </c>
-      <c r="AC41" s="11">
+      <c r="Z41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE41" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4391,7 +4723,15 @@
       <c r="Y42" s="11">
         <v>3</v>
       </c>
-      <c r="AC42" s="11">
+      <c r="Z42" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE42" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4477,7 +4817,15 @@
       <c r="Y43" s="11">
         <v>2</v>
       </c>
-      <c r="AC43" s="11">
+      <c r="Z43" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE43" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4563,10 +4911,18 @@
       <c r="Y44" s="11">
         <v>2</v>
       </c>
-      <c r="AB44" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="11">
+      <c r="Z44" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD44" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE44" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4652,10 +5008,18 @@
       <c r="Y45" s="11">
         <v>2</v>
       </c>
-      <c r="AB45" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="11">
+      <c r="Z45" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA45" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD45" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE45" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4744,6 +5108,14 @@
       <c r="Z46" s="11">
         <v>1</v>
       </c>
+      <c r="AA46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB46" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4">
@@ -4827,10 +5199,18 @@
       <c r="Y47" s="11">
         <v>3</v>
       </c>
-      <c r="AB47" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC47" s="11">
+      <c r="Z47" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD47" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4922,7 +5302,15 @@
       <c r="Z48" s="11">
         <v>1</v>
       </c>
-      <c r="AC48" s="11">
+      <c r="AA48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB48" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5014,7 +5402,15 @@
       <c r="Y49" s="11">
         <v>3</v>
       </c>
-      <c r="AB49" s="11">
+      <c r="Z49" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA49" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD49" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5106,6 +5502,14 @@
       <c r="Z50" s="11">
         <v>1</v>
       </c>
+      <c r="AA50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB50" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="4">
@@ -5195,7 +5599,15 @@
       <c r="Y51" s="11">
         <v>3</v>
       </c>
-      <c r="AB51" s="11">
+      <c r="Z51" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD51" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5287,7 +5699,15 @@
       <c r="Y52" s="11">
         <v>3</v>
       </c>
-      <c r="AB52" s="11">
+      <c r="Z52" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD52" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5376,7 +5796,15 @@
       <c r="Y53" s="11">
         <v>3</v>
       </c>
-      <c r="AB53" s="11">
+      <c r="Z53" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD53" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5465,7 +5893,15 @@
       <c r="Y54" s="11">
         <v>4</v>
       </c>
-      <c r="AB54" s="11">
+      <c r="Z54" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD54" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5557,7 +5993,15 @@
       <c r="Y55" s="11">
         <v>4</v>
       </c>
-      <c r="AB55" s="11">
+      <c r="Z55" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD55" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5649,7 +6093,15 @@
       <c r="Y56" s="11">
         <v>4</v>
       </c>
-      <c r="AB56" s="11">
+      <c r="Z56" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD56" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5741,7 +6193,15 @@
       <c r="Y57" s="11">
         <v>4</v>
       </c>
-      <c r="AB57" s="11">
+      <c r="Z57" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD57" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5833,7 +6293,15 @@
       <c r="Y58" s="11">
         <v>4</v>
       </c>
-      <c r="AB58" s="11">
+      <c r="Z58" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD58" s="11">
         <v>1</v>
       </c>
     </row>
@@ -5925,7 +6393,15 @@
       <c r="Y59" s="11">
         <v>4</v>
       </c>
-      <c r="AB59" s="11">
+      <c r="Z59" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD59" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6014,7 +6490,15 @@
       <c r="Y60" s="11">
         <v>3</v>
       </c>
-      <c r="AB60" s="11">
+      <c r="Z60" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD60" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6106,7 +6590,15 @@
       <c r="Y61" s="11">
         <v>2</v>
       </c>
-      <c r="AC61" s="11">
+      <c r="Z61" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA61" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE61" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6198,7 +6690,15 @@
       <c r="Y62" s="11">
         <v>2</v>
       </c>
-      <c r="AC62" s="11">
+      <c r="Z62" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE62" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6290,7 +6790,15 @@
       <c r="Y63" s="11">
         <v>3</v>
       </c>
-      <c r="AB63" s="11">
+      <c r="Z63" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD63" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6382,7 +6890,15 @@
       <c r="Y64" s="11">
         <v>3</v>
       </c>
-      <c r="AB64" s="11">
+      <c r="Z64" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD64" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6474,7 +6990,15 @@
       <c r="Y65" s="11">
         <v>3</v>
       </c>
-      <c r="AB65" s="11">
+      <c r="Z65" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD65" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6566,7 +7090,15 @@
       <c r="Y66" s="11">
         <v>3</v>
       </c>
-      <c r="AB66" s="11">
+      <c r="Z66" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD66" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6658,7 +7190,15 @@
       <c r="Y67" s="11">
         <v>3</v>
       </c>
-      <c r="AB67" s="11">
+      <c r="Z67" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD67" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6750,7 +7290,15 @@
       <c r="Y68" s="11">
         <v>3</v>
       </c>
-      <c r="AB68" s="11">
+      <c r="Z68" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA68" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD68" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6842,7 +7390,15 @@
       <c r="Y69" s="11">
         <v>4</v>
       </c>
-      <c r="AB69" s="11">
+      <c r="Z69" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA69" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD69" s="11">
         <v>1</v>
       </c>
     </row>
@@ -6934,7 +7490,15 @@
       <c r="Y70" s="11">
         <v>4</v>
       </c>
-      <c r="AB70" s="11">
+      <c r="Z70" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD70" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7026,7 +7590,15 @@
       <c r="Y71" s="11">
         <v>4</v>
       </c>
-      <c r="AB71" s="11">
+      <c r="Z71" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA71" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD71" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7118,7 +7690,15 @@
       <c r="Y72" s="11">
         <v>4</v>
       </c>
-      <c r="AB72" s="11">
+      <c r="Z72" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA72" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD72" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7210,7 +7790,15 @@
       <c r="Y73" s="11">
         <v>3</v>
       </c>
-      <c r="AB73" s="11">
+      <c r="Z73" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA73" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD73" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7302,7 +7890,15 @@
       <c r="Y74" s="11">
         <v>2</v>
       </c>
-      <c r="AB74" s="11">
+      <c r="Z74" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA74" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD74" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7394,7 +7990,15 @@
       <c r="Y75" s="11">
         <v>3</v>
       </c>
-      <c r="AB75" s="11">
+      <c r="Z75" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA75" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD75" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7486,7 +8090,15 @@
       <c r="Y76" s="11">
         <v>4</v>
       </c>
-      <c r="AB76" s="11">
+      <c r="Z76" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD76" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7578,7 +8190,15 @@
       <c r="Y77" s="11">
         <v>4</v>
       </c>
-      <c r="AB77" s="11">
+      <c r="Z77" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA77" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD77" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7670,7 +8290,15 @@
       <c r="Y78" s="11">
         <v>2</v>
       </c>
-      <c r="AB78" s="11">
+      <c r="Z78" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD78" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7762,7 +8390,15 @@
       <c r="Y79" s="11">
         <v>4</v>
       </c>
-      <c r="AB79" s="11">
+      <c r="Z79" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA79" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD79" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7854,7 +8490,15 @@
       <c r="Y80" s="11">
         <v>4</v>
       </c>
-      <c r="AB80" s="11">
+      <c r="Z80" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA80" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD80" s="11">
         <v>1</v>
       </c>
     </row>
@@ -7946,7 +8590,15 @@
       <c r="Y81" s="11">
         <v>4</v>
       </c>
-      <c r="AB81" s="11">
+      <c r="Z81" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA81" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD81" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8038,7 +8690,15 @@
       <c r="Y82" s="11">
         <v>4</v>
       </c>
-      <c r="AB82" s="11">
+      <c r="Z82" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA82" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD82" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8130,7 +8790,15 @@
       <c r="Y83" s="11">
         <v>3</v>
       </c>
-      <c r="AB83" s="11">
+      <c r="Z83" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA83" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD83" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8222,10 +8890,18 @@
       <c r="Y84" s="11">
         <v>4</v>
       </c>
-      <c r="AB84" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC84" s="11">
+      <c r="Z84" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA84" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD84" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE84" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8317,7 +8993,15 @@
       <c r="Y85" s="11">
         <v>2</v>
       </c>
-      <c r="AC85" s="11">
+      <c r="Z85" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE85" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8409,7 +9093,15 @@
       <c r="Y86" s="11">
         <v>3</v>
       </c>
-      <c r="AB86" s="11">
+      <c r="Z86" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA86" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD86" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8501,7 +9193,15 @@
       <c r="Y87" s="11">
         <v>2</v>
       </c>
-      <c r="AB87" s="11">
+      <c r="Z87" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA87" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD87" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8590,7 +9290,15 @@
       <c r="Y88" s="11">
         <v>2</v>
       </c>
-      <c r="AB88" s="11">
+      <c r="Z88" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD88" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8682,7 +9390,15 @@
       <c r="Y89" s="11">
         <v>3</v>
       </c>
-      <c r="AB89" s="11">
+      <c r="Z89" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA89" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD89" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8774,10 +9490,18 @@
       <c r="Y90" s="11">
         <v>3</v>
       </c>
-      <c r="AB90" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC90" s="11">
+      <c r="Z90" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA90" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD90" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE90" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8869,7 +9593,15 @@
       <c r="Y91" s="11">
         <v>3</v>
       </c>
-      <c r="AB91" s="11">
+      <c r="Z91" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA91" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD91" s="11">
         <v>1</v>
       </c>
     </row>
@@ -8961,7 +9693,15 @@
       <c r="Y92" s="11">
         <v>3</v>
       </c>
-      <c r="AB92" s="11">
+      <c r="Z92" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD92" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9053,7 +9793,15 @@
       <c r="Y93" s="11">
         <v>3</v>
       </c>
-      <c r="AB93" s="11">
+      <c r="Z93" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD93" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9145,7 +9893,15 @@
       <c r="Y94" s="11">
         <v>3</v>
       </c>
-      <c r="AB94" s="11">
+      <c r="Z94" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA94" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD94" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9237,7 +9993,15 @@
       <c r="Y95" s="11">
         <v>4</v>
       </c>
-      <c r="AB95" s="11">
+      <c r="Z95" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA95" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD95" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9329,7 +10093,15 @@
       <c r="Y96" s="11">
         <v>4</v>
       </c>
-      <c r="AB96" s="11">
+      <c r="Z96" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD96" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9421,7 +10193,15 @@
       <c r="Y97" s="11">
         <v>3</v>
       </c>
-      <c r="AB97" s="11">
+      <c r="Z97" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA97" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD97" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9513,7 +10293,15 @@
       <c r="Y98" s="11">
         <v>4</v>
       </c>
-      <c r="AB98" s="11">
+      <c r="Z98" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD98" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9605,7 +10393,15 @@
       <c r="Y99" s="11">
         <v>3</v>
       </c>
-      <c r="AB99" s="11">
+      <c r="Z99" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD99" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9697,7 +10493,15 @@
       <c r="Y100" s="11">
         <v>3</v>
       </c>
-      <c r="AB100" s="11">
+      <c r="Z100" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA100" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD100" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9789,7 +10593,15 @@
       <c r="Y101" s="11">
         <v>4</v>
       </c>
-      <c r="AB101" s="11">
+      <c r="Z101" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA101" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD101" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9875,7 +10687,15 @@
       <c r="X102" s="11">
         <v>0</v>
       </c>
-      <c r="AB102" s="11">
+      <c r="Z102" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA102" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD102" s="11">
         <v>1</v>
       </c>
     </row>
@@ -9967,7 +10787,15 @@
       <c r="Y103" s="11">
         <v>2</v>
       </c>
-      <c r="AB103" s="11">
+      <c r="Z103" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA103" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD103" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10059,7 +10887,15 @@
       <c r="Y104" s="11">
         <v>2</v>
       </c>
-      <c r="AC104" s="11">
+      <c r="Z104" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA104" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE104" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10151,7 +10987,15 @@
       <c r="Y105" s="11">
         <v>2</v>
       </c>
-      <c r="AB105" s="11">
+      <c r="Z105" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA105" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD105" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10243,7 +11087,15 @@
       <c r="Y106" s="11">
         <v>1</v>
       </c>
-      <c r="AB106" s="11">
+      <c r="Z106" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA106" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD106" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10323,7 +11175,15 @@
       <c r="Y107" s="11">
         <v>2</v>
       </c>
-      <c r="AB107" s="11">
+      <c r="Z107" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA107" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD107" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10409,7 +11269,15 @@
       <c r="X108" s="11">
         <v>0</v>
       </c>
-      <c r="AB108" s="11">
+      <c r="Z108" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA108" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD108" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10501,7 +11369,15 @@
       <c r="Y109" s="11">
         <v>4</v>
       </c>
-      <c r="AB109" s="11">
+      <c r="Z109" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA109" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD109" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10587,7 +11463,15 @@
       <c r="X110" s="11">
         <v>0</v>
       </c>
-      <c r="AB110" s="11">
+      <c r="Z110" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA110" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD110" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10679,7 +11563,15 @@
       <c r="Y111" s="11">
         <v>2</v>
       </c>
-      <c r="AB111" s="11">
+      <c r="Z111" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA111" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD111" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10771,7 +11663,15 @@
       <c r="Y112" s="11">
         <v>2</v>
       </c>
-      <c r="AB112" s="11">
+      <c r="Z112" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA112" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD112" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10863,7 +11763,15 @@
       <c r="Y113" s="11">
         <v>3</v>
       </c>
-      <c r="AB113" s="11">
+      <c r="Z113" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA113" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD113" s="11">
         <v>1</v>
       </c>
     </row>
@@ -10955,7 +11863,15 @@
       <c r="Y114" s="11">
         <v>3</v>
       </c>
-      <c r="AC114" s="11">
+      <c r="Z114" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA114" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE114" s="11">
         <v>1</v>
       </c>
     </row>
@@ -11047,7 +11963,15 @@
       <c r="Y115" s="11">
         <v>2</v>
       </c>
-      <c r="AB115" s="11">
+      <c r="Z115" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA115" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD115" s="11">
         <v>1</v>
       </c>
     </row>
@@ -11142,7 +12066,15 @@
       <c r="Z116" s="11">
         <v>1</v>
       </c>
-      <c r="AC116" s="11">
+      <c r="AA116" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB116" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE116" s="11">
         <v>1</v>
       </c>
     </row>
@@ -11237,6 +12169,14 @@
       <c r="Z117" s="11">
         <v>1</v>
       </c>
+      <c r="AA117" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AB117" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="4">
@@ -11326,13 +12266,21 @@
       <c r="Y118" s="11">
         <v>3</v>
       </c>
-      <c r="AB118" s="11">
+      <c r="Z118" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA118" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD118" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="4">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
@@ -11351,16 +12299,16 @@
         <v>7</v>
       </c>
       <c r="F119" s="7">
-        <v>43676</v>
+        <v>43655</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>19-53-LSSC05</t>
+          <t>19-50-LSSC05</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>E342</t>
+          <t>E341</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -11369,20 +12317,20 @@
         </is>
       </c>
       <c r="J119" s="8">
-        <v>0.354861111111111</v>
+        <v>0.415277777777778</v>
       </c>
       <c r="K119" s="9">
-        <v>9.7</v>
+        <v>10.3</v>
       </c>
       <c r="L119" s="9">
-        <v>24</v>
+        <v>22.20000076</v>
       </c>
       <c r="M119" s="9">
-        <v>709</v>
+        <v>504</v>
       </c>
       <c r="N119" s="9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="Q119" s="9" t="inlineStr">
@@ -11392,36 +12340,41 @@
       </c>
       <c r="R119" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>36</t>
         </is>
       </c>
       <c r="S119" s="9">
-        <v>54.90000153</v>
+        <v>39</v>
       </c>
       <c r="T119" s="9">
-        <v>0.7622</v>
+        <v>0.7583</v>
       </c>
       <c r="U119" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t/>
         </is>
       </c>
       <c r="V119" s="10">
-        <v>50</v>
-      </c>
-      <c r="X119" s="11">
+        <v>48</v>
+      </c>
+      <c r="Y119" s="11">
         <v>3</v>
       </c>
-      <c r="Y119" s="11">
-        <v>4</v>
-      </c>
-      <c r="AB119" s="11">
+      <c r="Z119" s="11">
+        <v>2</v>
+      </c>
+      <c r="AA119" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AD119" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
@@ -11437,19 +12390,19 @@
         <v>2019</v>
       </c>
       <c r="E120" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F120" s="7">
-        <v>43717</v>
+        <v>43676</v>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>20-07-LSSC01</t>
+          <t>19-53-LSSC05</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>E474</t>
+          <t>E342</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
@@ -11458,20 +12411,20 @@
         </is>
       </c>
       <c r="J120" s="8">
-        <v>0.359722222222222</v>
+        <v>0.354861111111111</v>
       </c>
       <c r="K120" s="9">
-        <v>8.7</v>
+        <v>9.7</v>
       </c>
       <c r="L120" s="9">
-        <v>22.79999924</v>
+        <v>24</v>
       </c>
       <c r="M120" s="9">
-        <v>598</v>
+        <v>709</v>
       </c>
       <c r="N120" s="9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="Q120" s="9" t="inlineStr">
@@ -11481,14 +12434,14 @@
       </c>
       <c r="R120" s="9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S120" s="9">
-        <v>23</v>
+        <v>54.90000153</v>
       </c>
       <c r="T120" s="9">
-        <v>0.2772</v>
+        <v>0.7622</v>
       </c>
       <c r="U120" s="5" t="inlineStr">
         <is>
@@ -11496,27 +12449,29 @@
         </is>
       </c>
       <c r="V120" s="10">
-        <v>37</v>
-      </c>
-      <c r="W120" s="9">
-        <v>0.00031</v>
+        <v>50</v>
       </c>
       <c r="X120" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y120" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB120" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC120" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z120" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA120" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD120" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
@@ -11535,16 +12490,16 @@
         <v>9</v>
       </c>
       <c r="F121" s="7">
-        <v>43718</v>
+        <v>43717</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>20-07-LSSC03</t>
+          <t>20-07-LSSC01</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>E475</t>
+          <t>E474</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -11553,20 +12508,20 @@
         </is>
       </c>
       <c r="J121" s="8">
-        <v>0.475694444444444</v>
+        <v>0.359722222222222</v>
       </c>
       <c r="K121" s="9">
-        <v>10.2</v>
+        <v>8.7</v>
       </c>
       <c r="L121" s="9">
-        <v>22.39999962</v>
+        <v>22.79999924</v>
       </c>
       <c r="M121" s="9">
-        <v>438.7999878</v>
+        <v>598</v>
       </c>
       <c r="N121" s="9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="Q121" s="9" t="inlineStr">
@@ -11576,14 +12531,14 @@
       </c>
       <c r="R121" s="9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>47</t>
         </is>
       </c>
       <c r="S121" s="9">
-        <v>25.29999924</v>
+        <v>23</v>
       </c>
       <c r="T121" s="9">
-        <v>0.7455</v>
+        <v>0.2772</v>
       </c>
       <c r="U121" s="5" t="inlineStr">
         <is>
@@ -11591,7 +12546,10 @@
         </is>
       </c>
       <c r="V121" s="10">
-        <v>50</v>
+        <v>37</v>
+      </c>
+      <c r="W121" s="9">
+        <v>0.00031</v>
       </c>
       <c r="X121" s="11">
         <v>1</v>
@@ -11599,13 +12557,24 @@
       <c r="Y121" s="11">
         <v>3</v>
       </c>
-      <c r="AB121" s="11">
+      <c r="Z121" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA121" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD121" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE121" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
@@ -11621,19 +12590,19 @@
         <v>2019</v>
       </c>
       <c r="E122" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F122" s="7">
-        <v>43767</v>
+        <v>43718</v>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>20-14-LSSC05</t>
+          <t>20-07-LSSC03</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>E476</t>
+          <t>E475</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -11642,20 +12611,20 @@
         </is>
       </c>
       <c r="J122" s="8">
-        <v>0.448611111111111</v>
+        <v>0.475694444444444</v>
       </c>
       <c r="K122" s="9">
-        <v>9.2</v>
+        <v>10.2</v>
       </c>
       <c r="L122" s="9">
-        <v>15.5</v>
+        <v>22.39999962</v>
       </c>
       <c r="M122" s="9">
-        <v>627</v>
+        <v>438.7999878</v>
       </c>
       <c r="N122" s="9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="Q122" s="9" t="inlineStr">
@@ -11665,14 +12634,14 @@
       </c>
       <c r="R122" s="9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>54</t>
         </is>
       </c>
       <c r="S122" s="9">
-        <v>69.59999847</v>
+        <v>25.29999924</v>
       </c>
       <c r="T122" s="9">
-        <v>0.442</v>
+        <v>0.7455</v>
       </c>
       <c r="U122" s="5" t="inlineStr">
         <is>
@@ -11680,10 +12649,7 @@
         </is>
       </c>
       <c r="V122" s="10">
-        <v>43</v>
-      </c>
-      <c r="W122" s="9">
-        <v>0.0015</v>
+        <v>50</v>
       </c>
       <c r="X122" s="11">
         <v>1</v>
@@ -11691,41 +12657,49 @@
       <c r="Y122" s="11">
         <v>3</v>
       </c>
-      <c r="AB122" s="11">
+      <c r="Z122" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA122" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD122" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>ELS</t>
+          <t>EDSM</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>MWT</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D123" s="6">
         <v>2019</v>
       </c>
       <c r="E123" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F123" s="7">
-        <v>43578</v>
+        <v>43767</v>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>19-39-SC01</t>
+          <t>20-14-LSSC05</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>0493</t>
+          <t>E476</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -11734,43 +12708,37 @@
         </is>
       </c>
       <c r="J123" s="8">
-        <v>0.420069444444444</v>
+        <v>0.448611111111111</v>
       </c>
       <c r="K123" s="9">
-        <v>9.50976</v>
+        <v>9.2</v>
       </c>
       <c r="L123" s="9">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="M123" s="9">
-        <v>786</v>
+        <v>627</v>
       </c>
       <c r="N123" s="9" t="inlineStr">
         <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="O123" s="9">
-        <v>18.3</v>
-      </c>
-      <c r="P123" s="9">
-        <v>786</v>
+          <t>0.29</t>
+        </is>
       </c>
       <c r="Q123" s="9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t/>
         </is>
       </c>
       <c r="R123" s="9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S123" s="9">
-        <v>17.4</v>
+        <v>69.59999847</v>
       </c>
       <c r="T123" s="9">
-        <v>0.0133</v>
+        <v>0.442</v>
       </c>
       <c r="U123" s="5" t="inlineStr">
         <is>
@@ -11778,21 +12746,32 @@
         </is>
       </c>
       <c r="V123" s="10">
-        <v>16.5</v>
+        <v>43</v>
+      </c>
+      <c r="W123" s="9">
+        <v>0.0015</v>
       </c>
       <c r="X123" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y123" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB123" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z123" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA123" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD123" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
@@ -11801,7 +12780,7 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>20mm</t>
+          <t>MWT</t>
         </is>
       </c>
       <c r="D124" s="6">
@@ -11811,16 +12790,16 @@
         <v>4</v>
       </c>
       <c r="F124" s="7">
-        <v>43559</v>
+        <v>43578</v>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>19-36-DI04</t>
+          <t>19-39-SC01</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>0493</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -11829,43 +12808,43 @@
         </is>
       </c>
       <c r="J124" s="8">
-        <v>0.487731481481481</v>
+        <v>0.420069444444444</v>
       </c>
       <c r="K124" s="9">
-        <v>10.45464</v>
+        <v>9.50976</v>
       </c>
       <c r="L124" s="9">
-        <v>13.8</v>
+        <v>15.4</v>
       </c>
       <c r="M124" s="9">
-        <v>136.5</v>
+        <v>786</v>
       </c>
       <c r="N124" s="9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="O124" s="9">
-        <v>13.9</v>
+        <v>18.3</v>
       </c>
       <c r="P124" s="9">
-        <v>137.5</v>
+        <v>786</v>
       </c>
       <c r="Q124" s="9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="R124" s="9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S124" s="9">
-        <v>28.9</v>
+        <v>17.4</v>
       </c>
       <c r="T124" s="9">
-        <v>0.0016</v>
+        <v>0.0133</v>
       </c>
       <c r="U124" s="5" t="inlineStr">
         <is>
@@ -11873,21 +12852,29 @@
         </is>
       </c>
       <c r="V124" s="10">
-        <v>11.3</v>
+        <v>16.5</v>
       </c>
       <c r="X124" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y124" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB124" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z124" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA124" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD124" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
@@ -11903,19 +12890,19 @@
         <v>2019</v>
       </c>
       <c r="E125" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F125" s="7">
-        <v>43606</v>
+        <v>43559</v>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>19-43-SC05</t>
+          <t>19-36-DI04</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>448</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -11924,40 +12911,43 @@
         </is>
       </c>
       <c r="J125" s="8">
-        <v>0.519328703703704</v>
+        <v>0.487731481481481</v>
+      </c>
+      <c r="K125" s="9">
+        <v>10.45464</v>
       </c>
       <c r="L125" s="9">
-        <v>17.4</v>
+        <v>13.8</v>
       </c>
       <c r="M125" s="9">
-        <v>730</v>
+        <v>136.5</v>
       </c>
       <c r="N125" s="9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="O125" s="9">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="P125" s="9">
-        <v>737</v>
+        <v>137.5</v>
       </c>
       <c r="Q125" s="9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="R125" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>59</t>
         </is>
       </c>
       <c r="S125" s="9">
-        <v>47.7</v>
+        <v>28.9</v>
       </c>
       <c r="T125" s="9">
-        <v>0.1327</v>
+        <v>0.0016</v>
       </c>
       <c r="U125" s="5" t="inlineStr">
         <is>
@@ -11965,25 +12955,33 @@
         </is>
       </c>
       <c r="V125" s="10">
-        <v>27</v>
+        <v>11.3</v>
       </c>
       <c r="X125" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y125" s="11">
         <v>3</v>
       </c>
-      <c r="Y125" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB125" s="11">
+      <c r="Z125" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA125" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD125" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>EDSM</t>
+          <t>ELS</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -11992,22 +12990,22 @@
         </is>
       </c>
       <c r="D126" s="6">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E126" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F126" s="7">
-        <v>43984</v>
+        <v>43606</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>20-45-LSSC03</t>
+          <t>19-43-SC05</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>LV1</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
@@ -12016,37 +13014,40 @@
         </is>
       </c>
       <c r="J126" s="8">
-        <v>0.351203703703704</v>
-      </c>
-      <c r="K126" s="9">
-        <v>8.382</v>
+        <v>0.519328703703704</v>
       </c>
       <c r="L126" s="9">
-        <v>22</v>
+        <v>17.4</v>
       </c>
       <c r="M126" s="9">
-        <v>506</v>
+        <v>730</v>
       </c>
       <c r="N126" s="9" t="inlineStr">
         <is>
-          <t>0.23</t>
-        </is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="O126" s="9">
+        <v>17.4</v>
+      </c>
+      <c r="P126" s="9">
+        <v>737</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.34</t>
         </is>
       </c>
       <c r="R126" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S126" s="9">
-        <v>48.2</v>
+        <v>47.7</v>
       </c>
       <c r="T126" s="9">
-        <v>0.4402</v>
+        <v>0.1327</v>
       </c>
       <c r="U126" s="5" t="inlineStr">
         <is>
@@ -12054,10 +13055,7 @@
         </is>
       </c>
       <c r="V126" s="10">
-        <v>38</v>
-      </c>
-      <c r="W126" s="9">
-        <v>0.00542</v>
+        <v>27</v>
       </c>
       <c r="X126" s="11">
         <v>3</v>
@@ -12065,13 +13063,21 @@
       <c r="Y126" s="11">
         <v>2</v>
       </c>
-      <c r="AB126" s="11">
+      <c r="Z126" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA126" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD126" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
@@ -12080,26 +13086,26 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>20mm</t>
         </is>
       </c>
       <c r="D127" s="6">
         <v>2020</v>
       </c>
       <c r="E127" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F127" s="7">
-        <v>44049</v>
+        <v>43984</v>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>21-02-LSR03</t>
+          <t>20-45-LSSC03</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>E207</t>
+          <t>LV1</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
@@ -12108,20 +13114,20 @@
         </is>
       </c>
       <c r="J127" s="8">
-        <v>0.426388888888889</v>
+        <v>0.351203703703704</v>
       </c>
       <c r="K127" s="9">
-        <v>9.3</v>
+        <v>8.382</v>
       </c>
       <c r="L127" s="9">
-        <v>21.89999962</v>
+        <v>22</v>
       </c>
       <c r="M127" s="9">
-        <v>2027</v>
+        <v>506</v>
       </c>
       <c r="N127" s="9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="Q127" s="9" t="inlineStr">
@@ -12131,14 +13137,14 @@
       </c>
       <c r="R127" s="9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S127" s="9">
-        <v>22.60000038</v>
+        <v>48.2</v>
       </c>
       <c r="T127" s="9">
-        <v>0.9344</v>
+        <v>0.4402</v>
       </c>
       <c r="U127" s="5" t="inlineStr">
         <is>
@@ -12146,24 +13152,32 @@
         </is>
       </c>
       <c r="V127" s="10">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="W127" s="9">
-        <v>0.0053</v>
+        <v>0.00542</v>
       </c>
       <c r="X127" s="11">
         <v>3</v>
       </c>
       <c r="Y127" s="11">
-        <v>3</v>
-      </c>
-      <c r="AC127" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z127" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA127" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD127" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
@@ -12179,19 +13193,19 @@
         <v>2020</v>
       </c>
       <c r="E128" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F128" s="7">
-        <v>44020</v>
+        <v>44049</v>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>20-50-LSR01</t>
+          <t>21-02-LSR03</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>E220</t>
+          <t>E207</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
@@ -12200,20 +13214,20 @@
         </is>
       </c>
       <c r="J128" s="8">
-        <v>0.43125</v>
+        <v>0.426388888888889</v>
       </c>
       <c r="K128" s="9">
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="L128" s="9">
-        <v>22.10000038</v>
+        <v>21.89999962</v>
       </c>
       <c r="M128" s="9">
-        <v>653</v>
+        <v>2027</v>
       </c>
       <c r="N128" s="9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="Q128" s="9" t="inlineStr">
@@ -12223,14 +13237,14 @@
       </c>
       <c r="R128" s="9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>60</t>
         </is>
       </c>
       <c r="S128" s="9">
-        <v>57.40000153</v>
+        <v>22.60000038</v>
       </c>
       <c r="T128" s="9">
-        <v>0.7253</v>
+        <v>0.9344</v>
       </c>
       <c r="U128" s="5" t="inlineStr">
         <is>
@@ -12238,24 +13252,32 @@
         </is>
       </c>
       <c r="V128" s="10">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="W128" s="9">
-        <v>0.00811</v>
+        <v>0.0053</v>
       </c>
       <c r="X128" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y128" s="11">
-        <v>2</v>
-      </c>
-      <c r="AC128" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z128" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA128" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE128" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
@@ -12274,16 +13296,16 @@
         <v>7</v>
       </c>
       <c r="F129" s="7">
-        <v>44018</v>
+        <v>44020</v>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>20-50-LSSC01</t>
+          <t>20-50-LSR01</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>E225</t>
+          <t>E220</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
@@ -12292,20 +13314,20 @@
         </is>
       </c>
       <c r="J129" s="8">
-        <v>0.421527777777778</v>
+        <v>0.43125</v>
       </c>
       <c r="K129" s="9">
-        <v>10.3</v>
+        <v>8.3</v>
       </c>
       <c r="L129" s="9">
-        <v>23</v>
+        <v>22.10000038</v>
       </c>
       <c r="M129" s="9">
-        <v>205.5</v>
+        <v>653</v>
       </c>
       <c r="N129" s="9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="Q129" s="9" t="inlineStr">
@@ -12315,14 +13337,14 @@
       </c>
       <c r="R129" s="9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S129" s="9">
-        <v>21</v>
+        <v>57.40000153</v>
       </c>
       <c r="T129" s="9">
-        <v>0.6629</v>
+        <v>0.7253</v>
       </c>
       <c r="U129" s="5" t="inlineStr">
         <is>
@@ -12330,24 +13352,32 @@
         </is>
       </c>
       <c r="V129" s="10">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W129" s="9">
-        <v>0.0024</v>
+        <v>0.00811</v>
       </c>
       <c r="X129" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y129" s="11">
         <v>2</v>
       </c>
-      <c r="AB129" s="11">
+      <c r="Z129" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA129" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE129" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
@@ -12366,16 +13396,16 @@
         <v>7</v>
       </c>
       <c r="F130" s="7">
-        <v>44019</v>
+        <v>44018</v>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>20-50-LSSC05</t>
+          <t>20-50-LSSC01</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>E227</t>
+          <t>E225</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
@@ -12384,20 +13414,20 @@
         </is>
       </c>
       <c r="J130" s="8">
-        <v>0.4125</v>
+        <v>0.421527777777778</v>
       </c>
       <c r="K130" s="9">
         <v>10.3</v>
       </c>
       <c r="L130" s="9">
-        <v>22.60000038</v>
+        <v>23</v>
       </c>
       <c r="M130" s="9">
-        <v>343.5</v>
+        <v>205.5</v>
       </c>
       <c r="N130" s="9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="Q130" s="9" t="inlineStr">
@@ -12407,14 +13437,14 @@
       </c>
       <c r="R130" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="S130" s="9">
-        <v>43.20000076</v>
+        <v>21</v>
       </c>
       <c r="T130" s="9">
-        <v>0.5672</v>
+        <v>0.6629</v>
       </c>
       <c r="U130" s="5" t="inlineStr">
         <is>
@@ -12422,52 +13452,60 @@
         </is>
       </c>
       <c r="V130" s="10">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W130" s="9">
-        <v>0.0057</v>
+        <v>0.0024</v>
       </c>
       <c r="X130" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y130" s="11">
         <v>2</v>
       </c>
-      <c r="AC130" s="11">
+      <c r="Z130" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA130" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD130" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>DJFMP</t>
+          <t>EDSM</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>MWT</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D131" s="6">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E131" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F131" s="7">
-        <v>44559</v>
+        <v>44019</v>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>SB018N</t>
+          <t>20-50-LSSC05</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>S-1</t>
+          <t>E227</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
@@ -12476,17 +13514,20 @@
         </is>
       </c>
       <c r="J131" s="8">
-        <v>0.324305555555556</v>
+        <v>0.4125</v>
+      </c>
+      <c r="K131" s="9">
+        <v>10.3</v>
       </c>
       <c r="L131" s="9">
-        <v>8.9</v>
+        <v>22.60000038</v>
       </c>
       <c r="M131" s="9">
-        <v>426.2</v>
+        <v>343.5</v>
       </c>
       <c r="N131" s="9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="Q131" s="9" t="inlineStr">
@@ -12496,14 +13537,14 @@
       </c>
       <c r="R131" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S131" s="9">
-        <v>55.4</v>
+        <v>43.20000076</v>
       </c>
       <c r="T131" s="9">
-        <v>3.5408</v>
+        <v>0.5672</v>
       </c>
       <c r="U131" s="5" t="inlineStr">
         <is>
@@ -12511,36 +13552,41 @@
         </is>
       </c>
       <c r="V131" s="10">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="W131" s="9">
-        <v>0.02222</v>
+        <v>0.0057</v>
       </c>
       <c r="X131" s="11">
         <v>3</v>
       </c>
       <c r="Y131" s="11">
-        <v>4</v>
-      </c>
-      <c r="AA131" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB131" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z131" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA131" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE131" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>EDSM</t>
+          <t>DJFMP</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>MWT</t>
         </is>
       </c>
       <c r="D132" s="6">
@@ -12550,16 +13596,16 @@
         <v>12</v>
       </c>
       <c r="F132" s="7">
-        <v>44553</v>
+        <v>44559</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>22-21-RV02</t>
+          <t>SB018N</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>S-108</t>
+          <t>S-1</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
@@ -12568,20 +13614,17 @@
         </is>
       </c>
       <c r="J132" s="8">
-        <v>0.386805555555556</v>
-      </c>
-      <c r="K132" s="9">
-        <v>17.3</v>
+        <v>0.324305555555556</v>
       </c>
       <c r="L132" s="9">
-        <v>8.600000381</v>
+        <v>8.9</v>
       </c>
       <c r="M132" s="9">
-        <v>410</v>
+        <v>426.2</v>
       </c>
       <c r="N132" s="9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="Q132" s="9" t="inlineStr">
@@ -12591,14 +13634,14 @@
       </c>
       <c r="R132" s="9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S132" s="9">
-        <v>37.59999847</v>
+        <v>55.4</v>
       </c>
       <c r="T132" s="9">
-        <v>1.2486</v>
+        <v>3.5408</v>
       </c>
       <c r="U132" s="5" t="inlineStr">
         <is>
@@ -12606,10 +13649,10 @@
         </is>
       </c>
       <c r="V132" s="10">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="W132" s="9">
-        <v>0.00623</v>
+        <v>0.02222</v>
       </c>
       <c r="X132" s="11">
         <v>3</v>
@@ -12617,13 +13660,24 @@
       <c r="Y132" s="11">
         <v>4</v>
       </c>
-      <c r="AA132" s="11">
+      <c r="Z132" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA132" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC132" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD132" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
@@ -12642,16 +13696,16 @@
         <v>12</v>
       </c>
       <c r="F133" s="7">
-        <v>44551</v>
+        <v>44553</v>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>22-21-USSC02</t>
+          <t>22-21-RV02</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>S-107</t>
+          <t>S-108</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -12660,20 +13714,20 @@
         </is>
       </c>
       <c r="J133" s="8">
-        <v>0.431944444444444</v>
+        <v>0.386805555555556</v>
       </c>
       <c r="K133" s="9">
-        <v>11.3</v>
+        <v>17.3</v>
       </c>
       <c r="L133" s="9">
-        <v>10.60000038</v>
+        <v>8.600000381</v>
       </c>
       <c r="M133" s="9">
-        <v>1113</v>
+        <v>410</v>
       </c>
       <c r="N133" s="9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="Q133" s="9" t="inlineStr">
@@ -12683,14 +13737,14 @@
       </c>
       <c r="R133" s="9" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>31</t>
         </is>
       </c>
       <c r="S133" s="9">
-        <v>15.5</v>
+        <v>37.59999847</v>
       </c>
       <c r="T133" s="9">
-        <v>1.8571</v>
+        <v>1.2486</v>
       </c>
       <c r="U133" s="5" t="inlineStr">
         <is>
@@ -12698,10 +13752,10 @@
         </is>
       </c>
       <c r="V133" s="10">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W133" s="9">
-        <v>0.00451</v>
+        <v>0.00623</v>
       </c>
       <c r="X133" s="11">
         <v>3</v>
@@ -12709,13 +13763,21 @@
       <c r="Y133" s="11">
         <v>4</v>
       </c>
-      <c r="AA133" s="11">
+      <c r="Z133" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA133" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC133" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
@@ -12734,16 +13796,16 @@
         <v>12</v>
       </c>
       <c r="F134" s="7">
-        <v>44557</v>
+        <v>44551</v>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>22-22-LSR01</t>
+          <t>22-21-USSC02</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>S-110</t>
+          <t>S-107</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -12752,20 +13814,20 @@
         </is>
       </c>
       <c r="J134" s="8">
-        <v>0.402083333333333</v>
+        <v>0.431944444444444</v>
       </c>
       <c r="K134" s="9">
-        <v>9.8</v>
+        <v>11.3</v>
       </c>
       <c r="L134" s="9">
-        <v>8.800000191</v>
+        <v>10.60000038</v>
       </c>
       <c r="M134" s="9">
-        <v>541</v>
+        <v>1113</v>
       </c>
       <c r="N134" s="9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="Q134" s="9" t="inlineStr">
@@ -12775,14 +13837,14 @@
       </c>
       <c r="R134" s="9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>131</t>
         </is>
       </c>
       <c r="S134" s="9">
-        <v>38.79999924</v>
+        <v>15.5</v>
       </c>
       <c r="T134" s="9">
-        <v>4.227</v>
+        <v>1.8571</v>
       </c>
       <c r="U134" s="5" t="inlineStr">
         <is>
@@ -12790,24 +13852,32 @@
         </is>
       </c>
       <c r="V134" s="10">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="W134" s="9">
-        <v>0.00499</v>
+        <v>0.00451</v>
       </c>
       <c r="X134" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y134" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB134" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z134" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA134" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC134" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
@@ -12820,22 +13890,22 @@
         </is>
       </c>
       <c r="D135" s="6">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E135" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F135" s="7">
-        <v>44566</v>
+        <v>44557</v>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>22-23-RV04</t>
+          <t>22-22-LSR01</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>S-113</t>
+          <t>S-110</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
@@ -12844,11 +13914,20 @@
         </is>
       </c>
       <c r="J135" s="8">
-        <v>0.502777777777778</v>
+        <v>0.402083333333333</v>
+      </c>
+      <c r="K135" s="9">
+        <v>9.8</v>
+      </c>
+      <c r="L135" s="9">
+        <v>8.800000191</v>
+      </c>
+      <c r="M135" s="9">
+        <v>541</v>
       </c>
       <c r="N135" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.25</t>
         </is>
       </c>
       <c r="Q135" s="9" t="inlineStr">
@@ -12858,11 +13937,14 @@
       </c>
       <c r="R135" s="9" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="S135" s="9">
+        <v>38.79999924</v>
       </c>
       <c r="T135" s="9">
-        <v>1.7199</v>
+        <v>4.227</v>
       </c>
       <c r="U135" s="5" t="inlineStr">
         <is>
@@ -12870,24 +13952,32 @@
         </is>
       </c>
       <c r="V135" s="10">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="W135" s="9">
-        <v>0.02112</v>
+        <v>0.00499</v>
       </c>
       <c r="X135" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y135" s="11">
         <v>3</v>
       </c>
-      <c r="AB135" s="11">
+      <c r="Z135" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA135" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD135" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
@@ -12906,16 +13996,16 @@
         <v>1</v>
       </c>
       <c r="F136" s="7">
-        <v>44592</v>
+        <v>44566</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>22-27-LSSC03</t>
+          <t>22-23-RV04</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>S-116</t>
+          <t>S-113</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -12924,20 +14014,11 @@
         </is>
       </c>
       <c r="J136" s="8">
-        <v>0.348611111111111</v>
-      </c>
-      <c r="K136" s="9">
-        <v>10.1</v>
-      </c>
-      <c r="L136" s="9">
-        <v>9.800000191</v>
-      </c>
-      <c r="M136" s="9">
-        <v>639</v>
+        <v>0.502777777777778</v>
       </c>
       <c r="N136" s="9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t/>
         </is>
       </c>
       <c r="Q136" s="9" t="inlineStr">
@@ -12947,14 +14028,11 @@
       </c>
       <c r="R136" s="9" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="S136" s="9">
-        <v>75.09999847</v>
+          <t/>
+        </is>
       </c>
       <c r="T136" s="9">
-        <v>2.5888</v>
+        <v>1.7199</v>
       </c>
       <c r="U136" s="5" t="inlineStr">
         <is>
@@ -12962,24 +14040,32 @@
         </is>
       </c>
       <c r="V136" s="10">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="W136" s="9">
-        <v>0.01997</v>
+        <v>0.02112</v>
       </c>
       <c r="X136" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y136" s="11">
-        <v>4</v>
-      </c>
-      <c r="AA136" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z136" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA136" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD136" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
@@ -12998,16 +14084,16 @@
         <v>1</v>
       </c>
       <c r="F137" s="7">
-        <v>44573</v>
+        <v>44592</v>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>22-24-LSSC03</t>
+          <t>22-27-LSSC03</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>S-119</t>
+          <t>S-116</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
@@ -13016,20 +14102,20 @@
         </is>
       </c>
       <c r="J137" s="8">
-        <v>0.408333333333333</v>
+        <v>0.348611111111111</v>
       </c>
       <c r="K137" s="9">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="L137" s="9">
-        <v>9.699999809</v>
+        <v>9.800000191</v>
       </c>
       <c r="M137" s="9">
-        <v>232.1000061</v>
+        <v>639</v>
       </c>
       <c r="N137" s="9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="Q137" s="9" t="inlineStr">
@@ -13039,14 +14125,14 @@
       </c>
       <c r="R137" s="9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S137" s="9">
-        <v>32.29999924</v>
+        <v>75.09999847</v>
       </c>
       <c r="T137" s="9">
-        <v>6.6357</v>
+        <v>2.5888</v>
       </c>
       <c r="U137" s="5" t="inlineStr">
         <is>
@@ -13054,33 +14140,41 @@
         </is>
       </c>
       <c r="V137" s="10">
-        <v>86</v>
+        <v>70</v>
+      </c>
+      <c r="W137" s="9">
+        <v>0.01997</v>
       </c>
       <c r="X137" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y137" s="11">
-        <v>3</v>
-      </c>
-      <c r="AA137" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB137" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z137" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC137" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>CVP</t>
+          <t>EDSM</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>KT</t>
         </is>
       </c>
       <c r="D138" s="6">
@@ -13090,16 +14184,16 @@
         <v>1</v>
       </c>
       <c r="F138" s="7">
-        <v>44577</v>
+        <v>44573</v>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>CVP</t>
+          <t>22-24-LSSC03</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>S-401</t>
+          <t>S-119</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
@@ -13108,14 +14202,20 @@
         </is>
       </c>
       <c r="J138" s="8">
-        <v>0.25</v>
+        <v>0.408333333333333</v>
+      </c>
+      <c r="K138" s="9">
+        <v>11.3</v>
       </c>
       <c r="L138" s="9">
-        <v>9.7</v>
+        <v>9.699999809</v>
+      </c>
+      <c r="M138" s="9">
+        <v>232.1000061</v>
       </c>
       <c r="N138" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.10</t>
         </is>
       </c>
       <c r="Q138" s="9" t="inlineStr">
@@ -13125,11 +14225,14 @@
       </c>
       <c r="R138" s="9" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="S138" s="9">
+        <v>32.29999924</v>
       </c>
       <c r="T138" s="9">
-        <v>0.466</v>
+        <v>6.6357</v>
       </c>
       <c r="U138" s="5" t="inlineStr">
         <is>
@@ -13137,49 +14240,60 @@
         </is>
       </c>
       <c r="V138" s="10">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="X138" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y138" s="11">
         <v>3</v>
       </c>
+      <c r="Z138" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA138" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AC138" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD138" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>EDSM</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t/>
         </is>
       </c>
       <c r="D139" s="6">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E139" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F139" s="7">
-        <v>44428</v>
+        <v>44577</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>22-03-LSSC02</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>E487</t>
+          <t>S-401</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
@@ -13188,20 +14302,14 @@
         </is>
       </c>
       <c r="J139" s="8">
-        <v>0.53125</v>
-      </c>
-      <c r="K139" s="9">
-        <v>11.1</v>
+        <v>0.25</v>
       </c>
       <c r="L139" s="9">
-        <v>22.10000038</v>
-      </c>
-      <c r="M139" s="9">
-        <v>323.6000061</v>
+        <v>9.7</v>
       </c>
       <c r="N139" s="9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t/>
         </is>
       </c>
       <c r="Q139" s="9" t="inlineStr">
@@ -13211,14 +14319,11 @@
       </c>
       <c r="R139" s="9" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="S139" s="9">
-        <v>25.5</v>
+          <t/>
+        </is>
       </c>
       <c r="T139" s="9">
-        <v>0.8197</v>
+        <v>0.466</v>
       </c>
       <c r="U139" s="5" t="inlineStr">
         <is>
@@ -13226,24 +14331,29 @@
         </is>
       </c>
       <c r="V139" s="10">
-        <v>52</v>
-      </c>
-      <c r="W139" s="9">
-        <v>0.00568</v>
+        <v>54</v>
       </c>
       <c r="X139" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y139" s="11">
         <v>3</v>
       </c>
-      <c r="Y139" s="11">
-        <v>4</v>
-      </c>
-      <c r="AA139" s="11">
+      <c r="Z139" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA139" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE139" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
@@ -13256,22 +14366,22 @@
         </is>
       </c>
       <c r="D140" s="6">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E140" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F140" s="7">
-        <v>44615</v>
+        <v>44428</v>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>22-30-SM03</t>
+          <t>22-03-LSSC02</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>S-008</t>
+          <t>E487</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
@@ -13280,20 +14390,20 @@
         </is>
       </c>
       <c r="J140" s="8">
-        <v>0.431944444444444</v>
+        <v>0.53125</v>
       </c>
       <c r="K140" s="9">
-        <v>4.7</v>
+        <v>11.1</v>
       </c>
       <c r="L140" s="9">
-        <v>10.10000038</v>
+        <v>22.10000038</v>
       </c>
       <c r="M140" s="9">
-        <v>3131</v>
+        <v>323.6000061</v>
       </c>
       <c r="N140" s="9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="Q140" s="9" t="inlineStr">
@@ -13303,14 +14413,14 @@
       </c>
       <c r="R140" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>49</t>
         </is>
       </c>
       <c r="S140" s="9">
-        <v>25.10000038</v>
+        <v>25.5</v>
       </c>
       <c r="T140" s="9">
-        <v>3.6947</v>
+        <v>0.8197</v>
       </c>
       <c r="U140" s="5" t="inlineStr">
         <is>
@@ -13318,24 +14428,32 @@
         </is>
       </c>
       <c r="V140" s="10">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="W140" s="9">
-        <v>0.02294</v>
+        <v>0.00568</v>
       </c>
       <c r="X140" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y140" s="11">
         <v>4</v>
       </c>
-      <c r="AB140" s="11">
+      <c r="Z140" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA140" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC140" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
@@ -13351,19 +14469,19 @@
         <v>2022</v>
       </c>
       <c r="E141" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F141" s="7">
-        <v>44631</v>
+        <v>44615</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>22-32-SM01</t>
+          <t>22-30-SM03</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>S-011</t>
+          <t>S-008</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
@@ -13372,11 +14490,20 @@
         </is>
       </c>
       <c r="J141" s="8">
-        <v>0.513888888888889</v>
+        <v>0.431944444444444</v>
+      </c>
+      <c r="K141" s="9">
+        <v>4.7</v>
+      </c>
+      <c r="L141" s="9">
+        <v>10.10000038</v>
+      </c>
+      <c r="M141" s="9">
+        <v>3131</v>
       </c>
       <c r="N141" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>1.61</t>
         </is>
       </c>
       <c r="Q141" s="9" t="inlineStr">
@@ -13386,11 +14513,14 @@
       </c>
       <c r="R141" s="9" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="S141" s="9">
+        <v>25.10000038</v>
       </c>
       <c r="T141" s="9">
-        <v>2.3332</v>
+        <v>3.6947</v>
       </c>
       <c r="U141" s="5" t="inlineStr">
         <is>
@@ -13398,24 +14528,32 @@
         </is>
       </c>
       <c r="V141" s="10">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="W141" s="9">
-        <v>0.0296</v>
+        <v>0.02294</v>
       </c>
       <c r="X141" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y141" s="11">
         <v>4</v>
       </c>
-      <c r="Y141" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB141" s="11">
+      <c r="Z141" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA141" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD141" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
@@ -13434,16 +14572,16 @@
         <v>3</v>
       </c>
       <c r="F142" s="7">
-        <v>44642</v>
+        <v>44631</v>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>22-34-SM01</t>
+          <t>22-32-SM01</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>S-13</t>
+          <t>S-011</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
@@ -13452,20 +14590,11 @@
         </is>
       </c>
       <c r="J142" s="8">
-        <v>0.51875</v>
-      </c>
-      <c r="K142" s="9">
-        <v>6.8</v>
-      </c>
-      <c r="L142" s="9">
-        <v>15.39999962</v>
-      </c>
-      <c r="M142" s="9">
-        <v>4335</v>
+        <v>0.513888888888889</v>
       </c>
       <c r="N142" s="9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t/>
         </is>
       </c>
       <c r="Q142" s="9" t="inlineStr">
@@ -13475,14 +14604,11 @@
       </c>
       <c r="R142" s="9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S142" s="9">
-        <v>90.40000153</v>
+          <t/>
+        </is>
       </c>
       <c r="T142" s="9">
-        <v>2.694</v>
+        <v>2.3332</v>
       </c>
       <c r="U142" s="5" t="inlineStr">
         <is>
@@ -13490,24 +14616,32 @@
         </is>
       </c>
       <c r="V142" s="10">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W142" s="9">
-        <v>0.02211</v>
+        <v>0.0296</v>
       </c>
       <c r="X142" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y142" s="11">
         <v>3</v>
       </c>
-      <c r="AB142" s="11">
+      <c r="Z142" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA142" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD142" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
@@ -13526,16 +14660,16 @@
         <v>3</v>
       </c>
       <c r="F143" s="7">
-        <v>44649</v>
+        <v>44642</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>22-35-SM01</t>
+          <t>22-34-SM01</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>S-14</t>
+          <t>S-13</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
@@ -13544,20 +14678,20 @@
         </is>
       </c>
       <c r="J143" s="8">
-        <v>0.465972222222222</v>
+        <v>0.51875</v>
       </c>
       <c r="K143" s="9">
-        <v>8.8</v>
+        <v>6.8</v>
       </c>
       <c r="L143" s="9">
-        <v>16.5</v>
+        <v>15.39999962</v>
       </c>
       <c r="M143" s="9">
-        <v>7902</v>
+        <v>4335</v>
       </c>
       <c r="N143" s="9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="Q143" s="9" t="inlineStr">
@@ -13567,14 +14701,14 @@
       </c>
       <c r="R143" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S143" s="9">
-        <v>93.69999695</v>
+        <v>90.40000153</v>
       </c>
       <c r="T143" s="9">
-        <v>2.7079</v>
+        <v>2.694</v>
       </c>
       <c r="U143" s="5" t="inlineStr">
         <is>
@@ -13582,24 +14716,32 @@
         </is>
       </c>
       <c r="V143" s="10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W143" s="9">
-        <v>0.02496</v>
+        <v>0.02211</v>
       </c>
       <c r="X143" s="11">
         <v>3</v>
       </c>
       <c r="Y143" s="11">
-        <v>4</v>
-      </c>
-      <c r="AB143" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z143" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA143" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD143" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
@@ -13615,19 +14757,19 @@
         <v>2022</v>
       </c>
       <c r="E144" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="7">
-        <v>44616</v>
+        <v>44649</v>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>22-30-LSSC01</t>
+          <t>22-35-SM01</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>S-120</t>
+          <t>S-14</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
@@ -13636,20 +14778,20 @@
         </is>
       </c>
       <c r="J144" s="8">
-        <v>0.520138888888889</v>
+        <v>0.465972222222222</v>
       </c>
       <c r="K144" s="9">
-        <v>11</v>
+        <v>8.8</v>
       </c>
       <c r="L144" s="9">
-        <v>11.19999981</v>
+        <v>16.5</v>
       </c>
       <c r="M144" s="9">
-        <v>386.7999878</v>
+        <v>7902</v>
       </c>
       <c r="N144" s="9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="Q144" s="9" t="inlineStr">
@@ -13659,14 +14801,14 @@
       </c>
       <c r="R144" s="9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S144" s="9">
-        <v>25.60000038</v>
+        <v>93.69999695</v>
       </c>
       <c r="T144" s="9">
-        <v>3.8923</v>
+        <v>2.7079</v>
       </c>
       <c r="U144" s="5" t="inlineStr">
         <is>
@@ -13674,24 +14816,32 @@
         </is>
       </c>
       <c r="V144" s="10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="W144" s="9">
-        <v>0.00263</v>
+        <v>0.02496</v>
       </c>
       <c r="X144" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y144" s="11">
-        <v>3</v>
-      </c>
-      <c r="AC144" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z144" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA144" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD144" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
@@ -13719,7 +14869,7 @@
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>S-121</t>
+          <t>S-120</t>
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr">
@@ -13758,7 +14908,7 @@
         <v>25.60000038</v>
       </c>
       <c r="T145" s="9">
-        <v>1.3369</v>
+        <v>3.8923</v>
       </c>
       <c r="U145" s="5" t="inlineStr">
         <is>
@@ -13766,10 +14916,10 @@
         </is>
       </c>
       <c r="V145" s="10">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="W145" s="9">
-        <v>0.0184</v>
+        <v>0.00263</v>
       </c>
       <c r="X145" s="11">
         <v>2</v>
@@ -13777,13 +14927,21 @@
       <c r="Y145" s="11">
         <v>3</v>
       </c>
-      <c r="AA145" s="11">
+      <c r="Z145" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA145" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE145" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
@@ -13811,7 +14969,7 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>S-122</t>
+          <t>S-121</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
@@ -13850,7 +15008,7 @@
         <v>25.60000038</v>
       </c>
       <c r="T146" s="9">
-        <v>1.8949</v>
+        <v>1.3369</v>
       </c>
       <c r="U146" s="5" t="inlineStr">
         <is>
@@ -13858,24 +15016,32 @@
         </is>
       </c>
       <c r="V146" s="10">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="W146" s="9">
-        <v>0.01126</v>
+        <v>0.0184</v>
       </c>
       <c r="X146" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y146" s="11">
         <v>3</v>
       </c>
-      <c r="Y146" s="11">
-        <v>4</v>
-      </c>
-      <c r="AA146" s="11">
+      <c r="Z146" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA146" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC146" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
@@ -13903,7 +15069,7 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>S-123</t>
+          <t>S-122</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
@@ -13912,20 +15078,20 @@
         </is>
       </c>
       <c r="J147" s="8">
-        <v>0.532638888888889</v>
+        <v>0.520138888888889</v>
       </c>
       <c r="K147" s="9">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="L147" s="9">
-        <v>11</v>
+        <v>11.19999981</v>
       </c>
       <c r="M147" s="9">
-        <v>396.5</v>
+        <v>386.7999878</v>
       </c>
       <c r="N147" s="9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="Q147" s="9" t="inlineStr">
@@ -13935,14 +15101,14 @@
       </c>
       <c r="R147" s="9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S147" s="9">
-        <v>30.10000038</v>
+        <v>25.60000038</v>
       </c>
       <c r="T147" s="9">
-        <v>1.7369</v>
+        <v>1.8949</v>
       </c>
       <c r="U147" s="5" t="inlineStr">
         <is>
@@ -13950,24 +15116,32 @@
         </is>
       </c>
       <c r="V147" s="10">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W147" s="9">
-        <v>0.00486</v>
+        <v>0.01126</v>
       </c>
       <c r="X147" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y147" s="11">
         <v>4</v>
       </c>
-      <c r="AA147" s="11">
+      <c r="Z147" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA147" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC147" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
@@ -13983,19 +15157,19 @@
         <v>2022</v>
       </c>
       <c r="E148" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F148" s="7">
-        <v>44628</v>
+        <v>44616</v>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>22-32-LSSC01</t>
+          <t>22-30-LSSC01</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>S-128</t>
+          <t>S-123</t>
         </is>
       </c>
       <c r="I148" s="5" t="inlineStr">
@@ -14004,20 +15178,20 @@
         </is>
       </c>
       <c r="J148" s="8">
-        <v>0.428472222222222</v>
+        <v>0.532638888888889</v>
       </c>
       <c r="K148" s="9">
-        <v>7.6</v>
+        <v>10.8</v>
       </c>
       <c r="L148" s="9">
-        <v>12.19999981</v>
+        <v>11</v>
       </c>
       <c r="M148" s="9">
-        <v>433.8999939</v>
+        <v>396.5</v>
       </c>
       <c r="N148" s="9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="Q148" s="9" t="inlineStr">
@@ -14027,14 +15201,14 @@
       </c>
       <c r="R148" s="9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S148" s="9">
-        <v>27.20000076</v>
+        <v>30.10000038</v>
       </c>
       <c r="T148" s="9">
-        <v>2.1016</v>
+        <v>1.7369</v>
       </c>
       <c r="U148" s="5" t="inlineStr">
         <is>
@@ -14042,24 +15216,32 @@
         </is>
       </c>
       <c r="V148" s="10">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W148" s="9">
-        <v>0.00644</v>
+        <v>0.00486</v>
       </c>
       <c r="X148" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y148" s="11">
         <v>4</v>
       </c>
-      <c r="AA148" s="11">
+      <c r="Z148" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA148" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC148" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
@@ -14087,7 +15269,7 @@
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>S-129</t>
+          <t>S-128</t>
         </is>
       </c>
       <c r="I149" s="5" t="inlineStr">
@@ -14126,7 +15308,7 @@
         <v>27.20000076</v>
       </c>
       <c r="T149" s="9">
-        <v>1.011</v>
+        <v>2.1016</v>
       </c>
       <c r="U149" s="5" t="inlineStr">
         <is>
@@ -14134,24 +15316,32 @@
         </is>
       </c>
       <c r="V149" s="10">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="W149" s="9">
-        <v>0.01005</v>
+        <v>0.00644</v>
       </c>
       <c r="X149" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y149" s="11">
         <v>4</v>
       </c>
-      <c r="AB149" s="11">
+      <c r="Z149" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA149" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC149" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
@@ -14179,7 +15369,7 @@
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>S-131</t>
+          <t>S-129</t>
         </is>
       </c>
       <c r="I150" s="5" t="inlineStr">
@@ -14218,7 +15408,7 @@
         <v>27.20000076</v>
       </c>
       <c r="T150" s="9">
-        <v>1.8063</v>
+        <v>1.011</v>
       </c>
       <c r="U150" s="5" t="inlineStr">
         <is>
@@ -14226,27 +15416,32 @@
         </is>
       </c>
       <c r="V150" s="10">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="W150" s="9">
-        <v>0.01878</v>
+        <v>0.01005</v>
       </c>
       <c r="X150" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y150" s="11">
         <v>4</v>
       </c>
-      <c r="AA150" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB150" s="11">
+      <c r="Z150" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA150" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD150" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
@@ -14274,7 +15469,7 @@
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>S-132</t>
+          <t>S-131</t>
         </is>
       </c>
       <c r="I151" s="5" t="inlineStr">
@@ -14313,7 +15508,7 @@
         <v>27.20000076</v>
       </c>
       <c r="T151" s="9">
-        <v>3.5917</v>
+        <v>1.8063</v>
       </c>
       <c r="U151" s="5" t="inlineStr">
         <is>
@@ -14321,27 +15516,35 @@
         </is>
       </c>
       <c r="V151" s="10">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="W151" s="9">
-        <v>0.0092</v>
+        <v>0.01878</v>
       </c>
       <c r="X151" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y151" s="11">
         <v>4</v>
       </c>
-      <c r="AA151" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB151" s="11">
+      <c r="Z151" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA151" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC151" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD151" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
@@ -14360,16 +15563,16 @@
         <v>3</v>
       </c>
       <c r="F152" s="7">
-        <v>44643</v>
+        <v>44628</v>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>22-34-USSC01</t>
+          <t>22-32-LSSC01</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>S-136</t>
+          <t>S-132</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
@@ -14378,20 +15581,20 @@
         </is>
       </c>
       <c r="J152" s="8">
-        <v>0.4</v>
+        <v>0.428472222222222</v>
       </c>
       <c r="K152" s="9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L152" s="9">
-        <v>14.5</v>
+        <v>12.19999981</v>
       </c>
       <c r="M152" s="9">
-        <v>905</v>
+        <v>433.8999939</v>
       </c>
       <c r="N152" s="9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="Q152" s="9" t="inlineStr">
@@ -14401,14 +15604,14 @@
       </c>
       <c r="R152" s="9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="S152" s="9">
-        <v>26.70000076</v>
+        <v>27.20000076</v>
       </c>
       <c r="T152" s="9">
-        <v>2.4354</v>
+        <v>3.5917</v>
       </c>
       <c r="U152" s="5" t="inlineStr">
         <is>
@@ -14416,21 +15619,35 @@
         </is>
       </c>
       <c r="V152" s="10">
-        <v>69</v>
+        <v>78</v>
+      </c>
+      <c r="W152" s="9">
+        <v>0.0092</v>
       </c>
       <c r="X152" s="11">
         <v>3</v>
       </c>
       <c r="Y152" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB152" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z152" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA152" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC152" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD152" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
@@ -14439,26 +15656,26 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>20mm</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D153" s="6">
         <v>2022</v>
       </c>
       <c r="E153" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F153" s="7">
-        <v>44656</v>
+        <v>44643</v>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>22-36-SB04</t>
+          <t>22-34-USSC01</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>S-136</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
@@ -14467,20 +15684,20 @@
         </is>
       </c>
       <c r="J153" s="8">
-        <v>0.492997685185185</v>
+        <v>0.4</v>
       </c>
       <c r="K153" s="9">
-        <v>8.13816</v>
+        <v>7.4</v>
       </c>
       <c r="L153" s="9">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="M153" s="9">
-        <v>3596</v>
+        <v>905</v>
       </c>
       <c r="N153" s="9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="Q153" s="9" t="inlineStr">
@@ -14490,14 +15707,14 @@
       </c>
       <c r="R153" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S153" s="9">
-        <v>119</v>
+        <v>26.70000076</v>
       </c>
       <c r="T153" s="9">
-        <v>0.0076</v>
+        <v>2.4354</v>
       </c>
       <c r="U153" s="5" t="inlineStr">
         <is>
@@ -14505,21 +15722,29 @@
         </is>
       </c>
       <c r="V153" s="10">
-        <v>15.7</v>
+        <v>69</v>
       </c>
       <c r="X153" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y153" s="11">
-        <v>2</v>
-      </c>
-      <c r="AC153" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z153" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA153" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD153" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
@@ -14528,26 +15753,26 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>20mm</t>
         </is>
       </c>
       <c r="D154" s="6">
         <v>2022</v>
       </c>
       <c r="E154" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F154" s="7">
-        <v>44788</v>
+        <v>44656</v>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>23-03-SSC06</t>
+          <t>22-36-SB04</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>S-204</t>
+          <t>525</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -14556,20 +15781,20 @@
         </is>
       </c>
       <c r="J154" s="8">
-        <v>0.527777777777778</v>
+        <v>0.492997685185185</v>
       </c>
       <c r="K154" s="9">
-        <v>8.4</v>
+        <v>8.13816</v>
       </c>
       <c r="L154" s="9">
-        <v>23.20000076</v>
+        <v>16</v>
       </c>
       <c r="M154" s="9">
-        <v>586</v>
+        <v>3596</v>
       </c>
       <c r="N154" s="9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="Q154" s="9" t="inlineStr">
@@ -14579,14 +15804,14 @@
       </c>
       <c r="R154" s="9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S154" s="9">
-        <v>46.5</v>
+        <v>119</v>
       </c>
       <c r="T154" s="9">
-        <v>0.7832</v>
+        <v>0.0076</v>
       </c>
       <c r="U154" s="5" t="inlineStr">
         <is>
@@ -14594,30 +15819,29 @@
         </is>
       </c>
       <c r="V154" s="10">
-        <v>52</v>
-      </c>
-      <c r="W154" s="9">
-        <v>0.0049</v>
+        <v>15.7</v>
       </c>
       <c r="X154" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y154" s="11">
-        <v>4</v>
-      </c>
-      <c r="AA154" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB154" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC154" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z154" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA154" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE154" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
@@ -14626,26 +15850,26 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>20mm</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D155" s="6">
         <v>2022</v>
       </c>
       <c r="E155" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F155" s="7">
-        <v>44684</v>
+        <v>44788</v>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>22-40-SSC03</t>
+          <t>23-03-SSC06</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>S-204</t>
         </is>
       </c>
       <c r="I155" s="5" t="inlineStr">
@@ -14654,20 +15878,20 @@
         </is>
       </c>
       <c r="J155" s="8">
-        <v>0.406956018518519</v>
+        <v>0.527777777777778</v>
       </c>
       <c r="K155" s="9">
-        <v>4.35864</v>
+        <v>8.4</v>
       </c>
       <c r="L155" s="9">
-        <v>16.9</v>
+        <v>23.20000076</v>
       </c>
       <c r="M155" s="9">
-        <v>656</v>
+        <v>586</v>
       </c>
       <c r="N155" s="9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="Q155" s="9" t="inlineStr">
@@ -14677,14 +15901,14 @@
       </c>
       <c r="R155" s="9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S155" s="9">
-        <v>68.4</v>
+        <v>46.5</v>
       </c>
       <c r="T155" s="9">
-        <v>0.1542</v>
+        <v>0.7832</v>
       </c>
       <c r="U155" s="5" t="inlineStr">
         <is>
@@ -14692,24 +15916,38 @@
         </is>
       </c>
       <c r="V155" s="10">
-        <v>29.1</v>
+        <v>52</v>
       </c>
       <c r="W155" s="9">
-        <v>0.00057</v>
+        <v>0.0049</v>
       </c>
       <c r="X155" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y155" s="11">
-        <v>2</v>
-      </c>
-      <c r="AA155" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z155" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA155" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AC155" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD155" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE155" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
       <c r="A156" s="4">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
@@ -14725,19 +15963,19 @@
         <v>2022</v>
       </c>
       <c r="E156" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F156" s="7">
-        <v>44671</v>
+        <v>44684</v>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>22-38-SM01</t>
+          <t>22-40-SSC03</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>434</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -14746,20 +15984,20 @@
         </is>
       </c>
       <c r="J156" s="8">
-        <v>0.365266203703704</v>
+        <v>0.406956018518519</v>
       </c>
       <c r="K156" s="9">
-        <v>7.1628</v>
+        <v>4.35864</v>
       </c>
       <c r="L156" s="9">
-        <v>15.8</v>
+        <v>16.9</v>
       </c>
       <c r="M156" s="9">
-        <v>4914</v>
+        <v>656</v>
       </c>
       <c r="N156" s="9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="Q156" s="9" t="inlineStr">
@@ -14769,14 +16007,14 @@
       </c>
       <c r="R156" s="9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S156" s="9">
-        <v>115</v>
+        <v>68.4</v>
       </c>
       <c r="T156" s="9">
-        <v>0.0035</v>
+        <v>0.1542</v>
       </c>
       <c r="U156" s="5" t="inlineStr">
         <is>
@@ -14784,13 +16022,24 @@
         </is>
       </c>
       <c r="V156" s="10">
-        <v>15.7</v>
+        <v>29.1</v>
+      </c>
+      <c r="W156" s="9">
+        <v>0.00057</v>
       </c>
       <c r="X156" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y156" s="11">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="Z156" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA156" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="AC156" s="11">
         <v>1</v>
@@ -14798,7 +16047,7 @@
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
@@ -14807,26 +16056,26 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>20mm</t>
         </is>
       </c>
       <c r="D157" s="6">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E157" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F157" s="7">
-        <v>44952</v>
+        <v>44671</v>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>23-26-CS01</t>
+          <t>22-38-SM01</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>S-209</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
@@ -14835,20 +16084,20 @@
         </is>
       </c>
       <c r="J157" s="8">
-        <v>0.365277777777778</v>
+        <v>0.365266203703704</v>
       </c>
       <c r="K157" s="9">
-        <v>12.1</v>
+        <v>7.1628</v>
       </c>
       <c r="L157" s="9">
-        <v>8.199999809</v>
+        <v>15.8</v>
       </c>
       <c r="M157" s="9">
-        <v>169.6000061</v>
+        <v>4914</v>
       </c>
       <c r="N157" s="9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="Q157" s="9" t="inlineStr">
@@ -14858,42 +16107,53 @@
       </c>
       <c r="R157" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S157" s="9">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="T157" s="9">
-        <v>4.1981</v>
+        <v>0.0035</v>
       </c>
       <c r="U157" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="V157" s="10">
-        <v>80</v>
+        <v>15.7</v>
       </c>
       <c r="X157" s="11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Y157" s="11">
+        <v>4</v>
       </c>
       <c r="Z157" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA157" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE157" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>CVP</t>
+          <t>EDSM</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>KT</t>
         </is>
       </c>
       <c r="D158" s="6">
@@ -14903,16 +16163,16 @@
         <v>1</v>
       </c>
       <c r="F158" s="7">
-        <v>44933</v>
+        <v>44952</v>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>CVP</t>
+          <t>23-26-CS01</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>S-405</t>
+          <t>S-209</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
@@ -14921,14 +16181,20 @@
         </is>
       </c>
       <c r="J158" s="8">
-        <v>0.583333333333333</v>
+        <v>0.365277777777778</v>
+      </c>
+      <c r="K158" s="9">
+        <v>12.1</v>
       </c>
       <c r="L158" s="9">
-        <v>10.5</v>
+        <v>8.199999809</v>
+      </c>
+      <c r="M158" s="9">
+        <v>169.6000061</v>
       </c>
       <c r="N158" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.07</t>
         </is>
       </c>
       <c r="Q158" s="9" t="inlineStr">
@@ -14938,39 +16204,41 @@
       </c>
       <c r="R158" s="9" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S158" s="9">
+        <v>120</v>
       </c>
       <c r="T158" s="9">
-        <v>1.4963</v>
+        <v>4.1981</v>
       </c>
       <c r="U158" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="V158" s="10">
-        <v>74</v>
-      </c>
-      <c r="W158" s="9">
-        <v>0.01089</v>
+        <v>80</v>
       </c>
       <c r="X158" s="11">
-        <v>3</v>
-      </c>
-      <c r="Y158" s="11">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Z158" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA158" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="AB158" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC158" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
@@ -14986,10 +16254,10 @@
         <v>2023</v>
       </c>
       <c r="E159" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" s="7">
-        <v>44971</v>
+        <v>44933</v>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
@@ -14998,7 +16266,7 @@
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>S-408</t>
+          <t>S-405</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
@@ -15010,7 +16278,7 @@
         <v>0.583333333333333</v>
       </c>
       <c r="L159" s="9">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="N159" s="9" t="inlineStr">
         <is>
@@ -15028,7 +16296,7 @@
         </is>
       </c>
       <c r="T159" s="9">
-        <v>0.8553</v>
+        <v>1.4963</v>
       </c>
       <c r="U159" s="5" t="inlineStr">
         <is>
@@ -15036,24 +16304,35 @@
         </is>
       </c>
       <c r="V159" s="10">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="W159" s="9">
-        <v>0.00213</v>
+        <v>0.01089</v>
       </c>
       <c r="X159" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y159" s="11">
-        <v>4</v>
-      </c>
-      <c r="AB159" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z159" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA159" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD159" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE159" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
@@ -15072,7 +16351,7 @@
         <v>2</v>
       </c>
       <c r="F160" s="7">
-        <v>44970</v>
+        <v>44971</v>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
@@ -15081,7 +16360,7 @@
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>S-409</t>
+          <t>S-408</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
@@ -15090,10 +16369,10 @@
         </is>
       </c>
       <c r="J160" s="8">
-        <v>0.833333333333333</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="L160" s="9">
-        <v>12.3333333333333</v>
+        <v>15</v>
       </c>
       <c r="N160" s="9" t="inlineStr">
         <is>
@@ -15111,7 +16390,7 @@
         </is>
       </c>
       <c r="T160" s="9">
-        <v>0.8053</v>
+        <v>0.8553</v>
       </c>
       <c r="U160" s="5" t="inlineStr">
         <is>
@@ -15119,21 +16398,32 @@
         </is>
       </c>
       <c r="V160" s="10">
-        <v>59</v>
+        <v>63</v>
+      </c>
+      <c r="W160" s="9">
+        <v>0.00213</v>
       </c>
       <c r="X160" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y160" s="11">
         <v>4</v>
       </c>
-      <c r="AB160" s="11">
+      <c r="Z160" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA160" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD160" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
@@ -15152,7 +16442,7 @@
         <v>2</v>
       </c>
       <c r="F161" s="7">
-        <v>44979</v>
+        <v>44970</v>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
@@ -15161,7 +16451,7 @@
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>S-411</t>
+          <t>S-409</t>
         </is>
       </c>
       <c r="I161" s="5" t="inlineStr">
@@ -15170,10 +16460,10 @@
         </is>
       </c>
       <c r="J161" s="8">
-        <v>0.999305555555556</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="L161" s="9">
-        <v>9.94444444444444</v>
+        <v>12.3333333333333</v>
       </c>
       <c r="N161" s="9" t="inlineStr">
         <is>
@@ -15191,7 +16481,7 @@
         </is>
       </c>
       <c r="T161" s="9">
-        <v>1.0693</v>
+        <v>0.8053</v>
       </c>
       <c r="U161" s="5" t="inlineStr">
         <is>
@@ -15199,7 +16489,7 @@
         </is>
       </c>
       <c r="V161" s="10">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="X161" s="11">
         <v>3</v>
@@ -15207,17 +16497,25 @@
       <c r="Y161" s="11">
         <v>4</v>
       </c>
-      <c r="AB161" s="11">
+      <c r="Z161" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA161" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD161" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>SWP</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -15232,16 +16530,16 @@
         <v>2</v>
       </c>
       <c r="F162" s="7">
-        <v>44965</v>
+        <v>44979</v>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>SWP</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>S-414</t>
+          <t>S-411</t>
         </is>
       </c>
       <c r="I162" s="5" t="inlineStr">
@@ -15250,10 +16548,10 @@
         </is>
       </c>
       <c r="J162" s="8">
-        <v>0.708333333333333</v>
+        <v>0.999305555555556</v>
       </c>
       <c r="L162" s="9">
-        <v>10.5555555555556</v>
+        <v>9.94444444444444</v>
       </c>
       <c r="N162" s="9" t="inlineStr">
         <is>
@@ -15271,7 +16569,7 @@
         </is>
       </c>
       <c r="T162" s="9">
-        <v>1.7972</v>
+        <v>1.0693</v>
       </c>
       <c r="U162" s="5" t="inlineStr">
         <is>
@@ -15279,52 +16577,57 @@
         </is>
       </c>
       <c r="V162" s="10">
-        <v>73</v>
-      </c>
-      <c r="W162" s="9">
-        <v>0.03289</v>
+        <v>65</v>
       </c>
       <c r="X162" s="11">
+        <v>3</v>
+      </c>
+      <c r="Y162" s="11">
         <v>4</v>
       </c>
-      <c r="Y162" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB162" s="11">
+      <c r="Z162" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA162" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD162" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>EDSM</t>
+          <t>SWP</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t/>
         </is>
       </c>
       <c r="D163" s="6">
         <v>2023</v>
       </c>
       <c r="E163" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F163" s="7">
-        <v>45194</v>
+        <v>44965</v>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>24-09-SM02</t>
+          <t>SWP</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>S-253</t>
+          <t>S-414</t>
         </is>
       </c>
       <c r="I163" s="5" t="inlineStr">
@@ -15333,20 +16636,14 @@
         </is>
       </c>
       <c r="J163" s="8">
-        <v>0.366666666666667</v>
-      </c>
-      <c r="K163" s="9">
-        <v>3.9</v>
+        <v>0.708333333333333</v>
       </c>
       <c r="L163" s="9">
-        <v>18.79999924</v>
-      </c>
-      <c r="M163" s="9">
-        <v>6651</v>
+        <v>10.5555555555556</v>
       </c>
       <c r="N163" s="9" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t/>
         </is>
       </c>
       <c r="Q163" s="9" t="inlineStr">
@@ -15356,14 +16653,11 @@
       </c>
       <c r="R163" s="9" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="S163" s="9">
-        <v>41.5</v>
+          <t/>
+        </is>
       </c>
       <c r="T163" s="9">
-        <v>0.6435</v>
+        <v>1.7972</v>
       </c>
       <c r="U163" s="5" t="inlineStr">
         <is>
@@ -15371,24 +16665,32 @@
         </is>
       </c>
       <c r="V163" s="10">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="W163" s="9">
-        <v>0.00689</v>
+        <v>0.03289</v>
       </c>
       <c r="X163" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y163" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB163" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z163" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA163" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD163" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
@@ -15407,38 +16709,38 @@
         <v>9</v>
       </c>
       <c r="F164" s="7">
-        <v>45197</v>
+        <v>45194</v>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>24-09-SB05</t>
+          <t>24-09-SM02</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
-          <t>S-254</t>
+          <t>S-253</t>
         </is>
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>DELSME x WAKASA</t>
+          <t>DELSME</t>
         </is>
       </c>
       <c r="J164" s="8">
-        <v>0.461111111111111</v>
+        <v>0.366666666666667</v>
       </c>
       <c r="K164" s="9">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="L164" s="9">
-        <v>19.60000038</v>
+        <v>18.79999924</v>
       </c>
       <c r="M164" s="9">
-        <v>9420</v>
+        <v>6651</v>
       </c>
       <c r="N164" s="9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="Q164" s="9" t="inlineStr">
@@ -15448,14 +16750,14 @@
       </c>
       <c r="R164" s="9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S164" s="9">
-        <v>45.79999924</v>
+        <v>41.5</v>
       </c>
       <c r="T164" s="9">
-        <v>2.0226</v>
+        <v>0.6435</v>
       </c>
       <c r="U164" s="5" t="inlineStr">
         <is>
@@ -15463,24 +16765,32 @@
         </is>
       </c>
       <c r="V164" s="10">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="W164" s="9">
-        <v>0.01075</v>
+        <v>0.00689</v>
       </c>
       <c r="X164" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y164" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB164" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z164" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA164" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD164" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
@@ -15496,41 +16806,41 @@
         <v>2023</v>
       </c>
       <c r="E165" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F165" s="7">
-        <v>44957</v>
+        <v>45197</v>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>23-27-LSJ06</t>
+          <t>24-09-SB05</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>S-403</t>
+          <t>S-254</t>
         </is>
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>DELSME</t>
+          <t>DELSME x WAKASA</t>
         </is>
       </c>
       <c r="J165" s="8">
-        <v>0.3875</v>
+        <v>0.461111111111111</v>
       </c>
       <c r="K165" s="9">
-        <v>17.4</v>
+        <v>6.4</v>
       </c>
       <c r="L165" s="9">
-        <v>8.5</v>
+        <v>19.60000038</v>
       </c>
       <c r="M165" s="9">
-        <v>242.6999969</v>
+        <v>9420</v>
       </c>
       <c r="N165" s="9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="Q165" s="9" t="inlineStr">
@@ -15540,14 +16850,14 @@
       </c>
       <c r="R165" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="S165" s="9">
-        <v>47.70000076</v>
+        <v>45.79999924</v>
       </c>
       <c r="T165" s="9">
-        <v>3.1539</v>
+        <v>2.0226</v>
       </c>
       <c r="U165" s="5" t="inlineStr">
         <is>
@@ -15555,24 +16865,32 @@
         </is>
       </c>
       <c r="V165" s="10">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="W165" s="9">
-        <v>0.01471</v>
+        <v>0.01075</v>
       </c>
       <c r="X165" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y165" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC165" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z165" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA165" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD165" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
@@ -15581,26 +16899,26 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t/>
+          <t>KT</t>
         </is>
       </c>
       <c r="D166" s="6">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E166" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" s="7">
-        <v>45327</v>
+        <v>44957</v>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>24-28-LSJ02</t>
+          <t>23-27-LSJ06</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
         <is>
-          <t>S-522</t>
+          <t>S-403</t>
         </is>
       </c>
       <c r="I166" s="5" t="inlineStr">
@@ -15608,9 +16926,21 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J166" s="8">
+        <v>0.3875</v>
+      </c>
+      <c r="K166" s="9">
+        <v>17.4</v>
+      </c>
+      <c r="L166" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="M166" s="9">
+        <v>242.6999969</v>
+      </c>
       <c r="N166" s="9" t="inlineStr">
         <is>
-          <t/>
+          <t>0.10</t>
         </is>
       </c>
       <c r="Q166" s="9" t="inlineStr">
@@ -15620,36 +16950,47 @@
       </c>
       <c r="R166" s="9" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S166" s="9">
+        <v>47.70000076</v>
       </c>
       <c r="T166" s="9">
-        <v>2.0623</v>
+        <v>3.1539</v>
       </c>
       <c r="U166" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="V166" s="10">
+        <v>73</v>
+      </c>
       <c r="W166" s="9">
-        <v>0.01193</v>
+        <v>0.01471</v>
       </c>
       <c r="X166" s="11">
         <v>2</v>
       </c>
       <c r="Y166" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB166" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC166" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z166" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA166" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE166" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
@@ -15677,7 +17018,7 @@
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>S-524</t>
+          <t>S-522</t>
         </is>
       </c>
       <c r="I167" s="5" t="inlineStr">
@@ -15701,7 +17042,7 @@
         </is>
       </c>
       <c r="T167" s="9">
-        <v>2.4292</v>
+        <v>2.0623</v>
       </c>
       <c r="U167" s="5" t="inlineStr">
         <is>
@@ -15709,21 +17050,32 @@
         </is>
       </c>
       <c r="W167" s="9">
-        <v>0.00842</v>
+        <v>0.01193</v>
       </c>
       <c r="X167" s="11">
         <v>2</v>
       </c>
       <c r="Y167" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB167" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z167" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA167" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD167" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE167" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
@@ -15742,16 +17094,16 @@
         <v>2</v>
       </c>
       <c r="F168" s="7">
-        <v>45330</v>
+        <v>45327</v>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>24-28-LSJ04</t>
+          <t>24-28-LSJ02</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
         <is>
-          <t>S-525</t>
+          <t>S-524</t>
         </is>
       </c>
       <c r="I168" s="5" t="inlineStr">
@@ -15775,7 +17127,7 @@
         </is>
       </c>
       <c r="T168" s="9">
-        <v>2.6062</v>
+        <v>2.4292</v>
       </c>
       <c r="U168" s="5" t="inlineStr">
         <is>
@@ -15783,21 +17135,29 @@
         </is>
       </c>
       <c r="W168" s="9">
-        <v>0.03461</v>
+        <v>0.00842</v>
       </c>
       <c r="X168" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y168" s="11">
-        <v>3</v>
-      </c>
-      <c r="AC168" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z168" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA168" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD168" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
@@ -15816,16 +17176,16 @@
         <v>2</v>
       </c>
       <c r="F169" s="7">
-        <v>45328</v>
+        <v>45330</v>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>24-28-SM02</t>
+          <t>24-28-LSJ04</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>S-237</t>
+          <t>S-525</t>
         </is>
       </c>
       <c r="I169" s="5" t="inlineStr">
@@ -15849,7 +17209,7 @@
         </is>
       </c>
       <c r="T169" s="9">
-        <v>2.6665</v>
+        <v>2.6062</v>
       </c>
       <c r="U169" s="5" t="inlineStr">
         <is>
@@ -15857,21 +17217,29 @@
         </is>
       </c>
       <c r="W169" s="9">
-        <v>0.02011</v>
+        <v>0.03461</v>
       </c>
       <c r="X169" s="11">
         <v>4</v>
       </c>
       <c r="Y169" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB169" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z169" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA169" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE169" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
@@ -15890,16 +17258,16 @@
         <v>2</v>
       </c>
       <c r="F170" s="7">
-        <v>45327</v>
+        <v>45328</v>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>24-28-SM01</t>
+          <t>24-28-SM02</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>S-260</t>
+          <t>S-237</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
@@ -15923,7 +17291,7 @@
         </is>
       </c>
       <c r="T170" s="9">
-        <v>1.0173</v>
+        <v>2.6665</v>
       </c>
       <c r="U170" s="5" t="inlineStr">
         <is>
@@ -15931,21 +17299,29 @@
         </is>
       </c>
       <c r="W170" s="9">
-        <v>0.0087</v>
+        <v>0.02011</v>
       </c>
       <c r="X170" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y170" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB170" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z170" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA170" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD170" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
@@ -15964,16 +17340,16 @@
         <v>2</v>
       </c>
       <c r="F171" s="7">
-        <v>45336</v>
+        <v>45327</v>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>24-29-SM02</t>
+          <t>24-28-SM01</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>S-239</t>
+          <t>S-260</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
@@ -15997,7 +17373,7 @@
         </is>
       </c>
       <c r="T171" s="9">
-        <v>1.795</v>
+        <v>1.0173</v>
       </c>
       <c r="U171" s="5" t="inlineStr">
         <is>
@@ -16005,21 +17381,29 @@
         </is>
       </c>
       <c r="W171" s="9">
-        <v>0.01468</v>
+        <v>0.0087</v>
       </c>
       <c r="X171" s="11">
         <v>3</v>
       </c>
       <c r="Y171" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB171" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z171" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA171" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD171" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
@@ -16042,12 +17426,12 @@
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>24-29-SM03</t>
+          <t>24-29-SM02</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>S-240</t>
+          <t>S-239</t>
         </is>
       </c>
       <c r="I172" s="5" t="inlineStr">
@@ -16071,7 +17455,7 @@
         </is>
       </c>
       <c r="T172" s="9">
-        <v>2.0944</v>
+        <v>1.795</v>
       </c>
       <c r="U172" s="5" t="inlineStr">
         <is>
@@ -16079,21 +17463,29 @@
         </is>
       </c>
       <c r="W172" s="9">
-        <v>0.01217</v>
+        <v>0.01468</v>
       </c>
       <c r="X172" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y172" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB172" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z172" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA172" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD172" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
@@ -16112,16 +17504,16 @@
         <v>2</v>
       </c>
       <c r="F173" s="7">
-        <v>45329</v>
+        <v>45336</v>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>24-28-SB03</t>
+          <t>24-29-SM03</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>LF-1300</t>
+          <t>S-240</t>
         </is>
       </c>
       <c r="I173" s="5" t="inlineStr">
@@ -16145,7 +17537,7 @@
         </is>
       </c>
       <c r="T173" s="9">
-        <v>2.9044</v>
+        <v>2.0944</v>
       </c>
       <c r="U173" s="5" t="inlineStr">
         <is>
@@ -16153,21 +17545,29 @@
         </is>
       </c>
       <c r="W173" s="9">
-        <v>0.00062</v>
+        <v>0.01217</v>
       </c>
       <c r="X173" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y173" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC173" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z173" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA173" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD173" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
@@ -16183,19 +17583,19 @@
         <v>2024</v>
       </c>
       <c r="E174" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F174" s="7">
-        <v>45362</v>
+        <v>45329</v>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>24-33-SSC03</t>
+          <t>24-28-SB03</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>S-332</t>
+          <t>LF-1300</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
@@ -16219,7 +17619,7 @@
         </is>
       </c>
       <c r="T174" s="9">
-        <v>2.31</v>
+        <v>2.9044</v>
       </c>
       <c r="U174" s="5" t="inlineStr">
         <is>
@@ -16227,21 +17627,29 @@
         </is>
       </c>
       <c r="W174" s="9">
-        <v>0.00948</v>
+        <v>0.00062</v>
       </c>
       <c r="X174" s="11">
         <v>1</v>
       </c>
       <c r="Y174" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB174" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z174" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA174" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE174" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
@@ -16260,16 +17668,16 @@
         <v>3</v>
       </c>
       <c r="F175" s="7">
-        <v>45364</v>
+        <v>45362</v>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>24-33-LSR02</t>
+          <t>24-33-SSC03</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>S-333</t>
+          <t>S-332</t>
         </is>
       </c>
       <c r="I175" s="5" t="inlineStr">
@@ -16293,7 +17701,7 @@
         </is>
       </c>
       <c r="T175" s="9">
-        <v>4.12</v>
+        <v>2.31</v>
       </c>
       <c r="U175" s="5" t="inlineStr">
         <is>
@@ -16301,7 +17709,7 @@
         </is>
       </c>
       <c r="W175" s="9">
-        <v>0.00311</v>
+        <v>0.00948</v>
       </c>
       <c r="X175" s="11">
         <v>1</v>
@@ -16309,13 +17717,21 @@
       <c r="Y175" s="11">
         <v>2</v>
       </c>
-      <c r="AB175" s="11">
+      <c r="Z175" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA175" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD175" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
@@ -16334,16 +17750,16 @@
         <v>3</v>
       </c>
       <c r="F176" s="7">
-        <v>45376</v>
+        <v>45364</v>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>24-35-LSR02</t>
+          <t>24-33-LSR02</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>S-334</t>
+          <t>S-333</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
@@ -16367,7 +17783,7 @@
         </is>
       </c>
       <c r="T176" s="9">
-        <v>3.65</v>
+        <v>4.12</v>
       </c>
       <c r="U176" s="5" t="inlineStr">
         <is>
@@ -16375,28 +17791,33 @@
         </is>
       </c>
       <c r="W176" s="9">
-        <v>0.01144</v>
+        <v>0.00311</v>
       </c>
       <c r="X176" s="11">
         <v>1</v>
       </c>
       <c r="Y176" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z176" s="11">
         <v>1</v>
       </c>
-      <c r="AB176" s="11">
+      <c r="AA176" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD176" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>CVP</t>
+          <t>EDSM</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -16408,19 +17829,19 @@
         <v>2024</v>
       </c>
       <c r="E177" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" s="7">
-        <v>45328</v>
+        <v>45376</v>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>CVP</t>
+          <t>24-35-LSR02</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>LF-1963</t>
+          <t>S-334</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
@@ -16444,7 +17865,7 @@
         </is>
       </c>
       <c r="T177" s="9">
-        <v>1.364</v>
+        <v>3.65</v>
       </c>
       <c r="U177" s="5" t="inlineStr">
         <is>
@@ -16452,21 +17873,32 @@
         </is>
       </c>
       <c r="W177" s="9">
-        <v>0.00271</v>
+        <v>0.01144</v>
       </c>
       <c r="X177" s="11">
         <v>1</v>
       </c>
       <c r="Y177" s="11">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="Z177" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA177" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="AB177" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD177" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
@@ -16485,7 +17917,7 @@
         <v>2</v>
       </c>
       <c r="F178" s="7">
-        <v>45331</v>
+        <v>45328</v>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
@@ -16494,7 +17926,7 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>LF-1964</t>
+          <t>LF-1963</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
@@ -16518,23 +17950,37 @@
         </is>
       </c>
       <c r="T178" s="9">
-        <v>2.74</v>
+        <v>1.364</v>
       </c>
       <c r="U178" s="5" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W178" s="9">
+        <v>0.00271</v>
       </c>
       <c r="X178" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC178" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y178" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z178" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA178" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD178" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
@@ -16553,7 +17999,7 @@
         <v>2</v>
       </c>
       <c r="F179" s="7">
-        <v>45334</v>
+        <v>45331</v>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
@@ -16562,7 +18008,7 @@
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>LF-1966</t>
+          <t>LF-1964</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
@@ -16586,29 +18032,31 @@
         </is>
       </c>
       <c r="T179" s="9">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="U179" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W179" s="9">
-        <v>0.00129</v>
+          <t>N</t>
+        </is>
       </c>
       <c r="X179" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y179" s="11">
-        <v>4</v>
-      </c>
-      <c r="AB179" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA179" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE179" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
@@ -16627,7 +18075,7 @@
         <v>2</v>
       </c>
       <c r="F180" s="7">
-        <v>45335</v>
+        <v>45334</v>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
@@ -16636,7 +18084,7 @@
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>LF-1968</t>
+          <t>LF-1966</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
@@ -16660,30 +18108,41 @@
         </is>
       </c>
       <c r="T180" s="9">
-        <v>3.34</v>
+        <v>1.55</v>
       </c>
       <c r="U180" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="W180" s="9">
+        <v>0.00129</v>
+      </c>
       <c r="X180" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y180" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB180" s="11">
+        <v>4</v>
+      </c>
+      <c r="Z180" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA180" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD180" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>EDSM</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
@@ -16695,19 +18154,19 @@
         <v>2024</v>
       </c>
       <c r="E181" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F181" s="7">
-        <v>45511</v>
+        <v>45335</v>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>25-02-SB04</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>S-341</t>
+          <t>LF-1968</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
@@ -16731,33 +18190,38 @@
         </is>
       </c>
       <c r="T181" s="9">
-        <v>0.894</v>
+        <v>3.34</v>
       </c>
       <c r="U181" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="W181" s="9">
-        <v>0.0071</v>
       </c>
       <c r="X181" s="11">
         <v>2</v>
       </c>
       <c r="Y181" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB181" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z181" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA181" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD181" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>CVP</t>
+          <t>EDSM</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -16766,78 +18230,80 @@
         </is>
       </c>
       <c r="D182" s="6">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E182" s="6">
+        <v>8</v>
+      </c>
+      <c r="F182" s="7">
+        <v>45511</v>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>25-02-SB04</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>S-341</t>
+        </is>
+      </c>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>DELSME</t>
+        </is>
+      </c>
+      <c r="N182" s="9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q182" s="9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R182" s="9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T182" s="9">
+        <v>0.894</v>
+      </c>
+      <c r="U182" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W182" s="9">
+        <v>0.0071</v>
+      </c>
+      <c r="X182" s="11">
         <v>2</v>
       </c>
-      <c r="F182" s="7">
-        <v>44975</v>
-      </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>CVP</t>
-        </is>
-      </c>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>S-620</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="inlineStr">
-        <is>
-          <t>DELSME</t>
-        </is>
-      </c>
-      <c r="J182" s="8">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="L182" s="9">
-        <v>10</v>
-      </c>
-      <c r="N182" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q182" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R182" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T182" s="9">
-        <v>2.106</v>
-      </c>
-      <c r="U182" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V182" s="10">
-        <v>76</v>
-      </c>
-      <c r="X182" s="11">
-        <v>1</v>
-      </c>
       <c r="Y182" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB182" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z182" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA182" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD182" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>DJFMP</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
@@ -16846,22 +18312,22 @@
         </is>
       </c>
       <c r="D183" s="6">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E183" s="6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F183" s="7">
-        <v>45645</v>
+        <v>44975</v>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>SR012B</t>
+          <t>CVP</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>S-284</t>
+          <t>S-620</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
@@ -16869,6 +18335,12 @@
           <t>DELSME</t>
         </is>
       </c>
+      <c r="J183" s="8">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="L183" s="9">
+        <v>10</v>
+      </c>
       <c r="N183" s="9" t="inlineStr">
         <is>
           <t/>
@@ -16885,30 +18357,41 @@
         </is>
       </c>
       <c r="T183" s="9">
-        <v>1.8841</v>
+        <v>2.106</v>
       </c>
       <c r="U183" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="V183" s="10">
+        <v>76</v>
+      </c>
       <c r="X183" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y183" s="11">
-        <v>3</v>
-      </c>
-      <c r="AB183" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z183" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA183" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD183" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>EDSM</t>
+          <t>DJFMP</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
@@ -16927,12 +18410,12 @@
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>25-21-LSR05</t>
+          <t>SR012B</t>
         </is>
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>S-271</t>
+          <t>S-284</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
@@ -16956,7 +18439,7 @@
         </is>
       </c>
       <c r="T184" s="9">
-        <v>2.6631</v>
+        <v>1.8841</v>
       </c>
       <c r="U184" s="5" t="inlineStr">
         <is>
@@ -16967,15 +18450,23 @@
         <v>4</v>
       </c>
       <c r="Y184" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB184" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z184" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA184" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD184" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
@@ -16994,16 +18485,16 @@
         <v>12</v>
       </c>
       <c r="F185" s="7">
-        <v>45657</v>
+        <v>45645</v>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>25-23-SB02</t>
+          <t>25-21-LSR05</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>S-346</t>
+          <t>S-271</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
@@ -17027,29 +18518,34 @@
         </is>
       </c>
       <c r="T185" s="9">
-        <v>2.2929</v>
+        <v>2.6631</v>
       </c>
       <c r="U185" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="W185" s="9">
-        <v>0.03958</v>
       </c>
       <c r="X185" s="11">
         <v>4</v>
       </c>
       <c r="Y185" s="11">
-        <v>3</v>
-      </c>
-      <c r="AC185" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z185" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA185" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AD185" s="11">
         <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4">
-        <v>703</v>
+        <v>654</v>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
@@ -17068,16 +18564,16 @@
         <v>12</v>
       </c>
       <c r="F186" s="7">
-        <v>45645</v>
+        <v>45657</v>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>25-21-LSR04</t>
+          <t>25-23-SB02</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>S-274</t>
+          <t>S-346</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
@@ -17101,7 +18597,7 @@
         </is>
       </c>
       <c r="T186" s="9">
-        <v>1.8687</v>
+        <v>2.2929</v>
       </c>
       <c r="U186" s="5" t="inlineStr">
         <is>
@@ -17109,15 +18605,105 @@
         </is>
       </c>
       <c r="W186" s="9">
-        <v>0.02281</v>
+        <v>0.03958</v>
       </c>
       <c r="X186" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y186" s="11">
         <v>3</v>
       </c>
-      <c r="AC186" s="11">
+      <c r="Z186" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA186" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE186" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="187">
+      <c r="A187" s="4">
+        <v>703</v>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>EDSM</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D187" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E187" s="6">
+        <v>12</v>
+      </c>
+      <c r="F187" s="7">
+        <v>45645</v>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>25-21-LSR04</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>S-274</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>DELSME</t>
+        </is>
+      </c>
+      <c r="N187" s="9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q187" s="9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R187" s="9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T187" s="9">
+        <v>1.8687</v>
+      </c>
+      <c r="U187" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W187" s="9">
+        <v>0.02281</v>
+      </c>
+      <c r="X187" s="11">
+        <v>3</v>
+      </c>
+      <c r="Y187" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z187" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA187" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AE187" s="11">
         <v>1</v>
       </c>
     </row>
